--- a/DOCS/UltimateSup_AI_Media_Workflows_Master_v2.xlsx
+++ b/DOCS/UltimateSup_AI_Media_Workflows_Master_v2.xlsx
@@ -4931,7 +4931,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5102,21 +5102,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5141,20 +5132,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -5187,21 +5169,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -5283,10 +5256,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5339,9 +5308,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -5351,18 +5317,12 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5527,12 +5487,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -6841,3531 +6795,3531 @@
   <dimension ref="A1:W116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="12.6176470588235" style="128" customWidth="1"/>
-    <col min="2" max="2" width="29.4044117647059" style="128" customWidth="1"/>
-    <col min="3" max="3" width="36" style="128" customWidth="1"/>
-    <col min="4" max="4" width="24" style="128" customWidth="1"/>
-    <col min="5" max="5" width="21" style="128" customWidth="1"/>
-    <col min="6" max="6" width="17" style="128" customWidth="1"/>
-    <col min="7" max="7" width="23.5294117647059" style="128" customWidth="1"/>
-    <col min="8" max="8" width="15" style="128" customWidth="1"/>
-    <col min="9" max="9" width="18" style="128" customWidth="1"/>
-    <col min="10" max="11" width="13" style="128" customWidth="1"/>
-    <col min="12" max="12" width="16" style="128" customWidth="1"/>
-    <col min="13" max="13" width="25" style="128" customWidth="1"/>
-    <col min="14" max="14" width="33" style="128" customWidth="1"/>
-    <col min="15" max="15" width="30" style="128" customWidth="1"/>
-    <col min="16" max="16" width="35" style="128" customWidth="1"/>
-    <col min="17" max="17" width="28" style="128" customWidth="1"/>
-    <col min="18" max="18" width="25" style="128" customWidth="1"/>
-    <col min="19" max="19" width="24" style="128" customWidth="1"/>
-    <col min="20" max="20" width="34" style="128" customWidth="1"/>
-    <col min="21" max="21" width="9" style="128"/>
-    <col min="22" max="22" width="28" style="128" customWidth="1"/>
-    <col min="23" max="23" width="12" style="128" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="128"/>
+    <col min="1" max="1" width="12.6176470588235" style="117" customWidth="1"/>
+    <col min="2" max="2" width="29.4044117647059" style="117" customWidth="1"/>
+    <col min="3" max="3" width="36" style="117" customWidth="1"/>
+    <col min="4" max="4" width="24" style="117" customWidth="1"/>
+    <col min="5" max="5" width="21" style="117" customWidth="1"/>
+    <col min="6" max="6" width="17" style="117" customWidth="1"/>
+    <col min="7" max="7" width="23.5294117647059" style="117" customWidth="1"/>
+    <col min="8" max="8" width="15" style="117" customWidth="1"/>
+    <col min="9" max="9" width="18" style="117" customWidth="1"/>
+    <col min="10" max="11" width="13" style="117" customWidth="1"/>
+    <col min="12" max="12" width="16" style="117" customWidth="1"/>
+    <col min="13" max="13" width="25" style="117" customWidth="1"/>
+    <col min="14" max="14" width="33" style="117" customWidth="1"/>
+    <col min="15" max="15" width="30" style="117" customWidth="1"/>
+    <col min="16" max="16" width="35" style="117" customWidth="1"/>
+    <col min="17" max="17" width="28" style="117" customWidth="1"/>
+    <col min="18" max="18" width="25" style="117" customWidth="1"/>
+    <col min="19" max="19" width="24" style="117" customWidth="1"/>
+    <col min="20" max="20" width="34" style="117" customWidth="1"/>
+    <col min="21" max="21" width="9" style="117"/>
+    <col min="22" max="22" width="28" style="117" customWidth="1"/>
+    <col min="23" max="23" width="12" style="117" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="117"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.2" spans="1:20">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
-      <c r="I1" s="129"/>
-      <c r="J1" s="129"/>
-      <c r="K1" s="129"/>
-      <c r="L1" s="129"/>
-      <c r="M1" s="129"/>
-      <c r="N1" s="129"/>
-      <c r="O1" s="129"/>
-      <c r="P1" s="129"/>
-      <c r="Q1" s="129"/>
-      <c r="R1" s="129"/>
-      <c r="S1" s="129"/>
-      <c r="T1" s="129"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="130"/>
-      <c r="Q2" s="130"/>
-      <c r="R2" s="130"/>
-      <c r="S2" s="130"/>
-      <c r="T2" s="130"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="119"/>
+      <c r="R2" s="119"/>
+      <c r="S2" s="119"/>
+      <c r="T2" s="119"/>
     </row>
     <row r="4" ht="17.6" spans="1:20">
-      <c r="A4" s="131" t="s">
+      <c r="A4" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="131"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="131"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="131"/>
-      <c r="T4" s="131"/>
+      <c r="B4" s="120"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="120"/>
+      <c r="G4" s="120"/>
+      <c r="H4" s="120"/>
+      <c r="I4" s="120"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120"/>
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120"/>
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="120"/>
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
     </row>
     <row r="5" ht="28" spans="1:20">
-      <c r="A5" s="132" t="s">
+      <c r="A5" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="133" t="s">
+      <c r="B5" s="122" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="134"/>
-      <c r="D5" s="135" t="s">
+      <c r="C5" s="123"/>
+      <c r="D5" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="136" t="str">
+      <c r="E5" s="125" t="str">
         <f>HYPERLINK("","Mở repository")</f>
         <v>Mở repository</v>
       </c>
     </row>
     <row r="6" ht="55" spans="1:20">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="139"/>
-      <c r="D6" s="140" t="s">
+      <c r="C6" s="128"/>
+      <c r="D6" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="141" t="s">
+      <c r="E6" s="130" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="41" spans="1:20">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="138" t="s">
+      <c r="B7" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="139"/>
-      <c r="D7" s="140" t="s">
+      <c r="C7" s="128"/>
+      <c r="D7" s="129" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="141" t="s">
+      <c r="E7" s="130" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" ht="41" spans="1:20">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="142" t="s">
+      <c r="B8" s="131" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="142"/>
-      <c r="D8" s="143" t="s">
+      <c r="C8" s="131"/>
+      <c r="D8" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="144" t="s">
+      <c r="E8" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="145"/>
-      <c r="G8" s="145"/>
-      <c r="H8" s="145"/>
-      <c r="I8" s="145"/>
-      <c r="J8" s="145"/>
-      <c r="K8" s="145"/>
-      <c r="L8" s="145"/>
-      <c r="M8" s="145"/>
-      <c r="N8" s="145"/>
-      <c r="O8" s="145"/>
-      <c r="P8" s="145"/>
-      <c r="Q8" s="145"/>
-      <c r="R8" s="145"/>
-      <c r="S8" s="145"/>
-      <c r="T8" s="145"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="133"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="133"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="133"/>
+      <c r="Q8" s="133"/>
+      <c r="R8" s="133"/>
+      <c r="S8" s="133"/>
+      <c r="T8" s="133"/>
     </row>
     <row r="9" ht="41" spans="1:20">
-      <c r="A9" s="137" t="s">
+      <c r="A9" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="142" t="s">
+      <c r="B9" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="142"/>
-      <c r="D9" s="143" t="s">
+      <c r="C9" s="131"/>
+      <c r="D9" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="144" t="s">
+      <c r="E9" s="132" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="145"/>
-      <c r="G9" s="145"/>
-      <c r="H9" s="145"/>
-      <c r="I9" s="145"/>
-      <c r="J9" s="145"/>
-      <c r="K9" s="145"/>
-      <c r="L9" s="145"/>
-      <c r="M9" s="145"/>
-      <c r="N9" s="145"/>
-      <c r="O9" s="145"/>
-      <c r="P9" s="145"/>
-      <c r="Q9" s="145"/>
-      <c r="R9" s="145"/>
-      <c r="S9" s="145"/>
-      <c r="T9" s="145"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="133"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="133"/>
+      <c r="T9" s="133"/>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="138" t="s">
+      <c r="B10" s="127" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="139"/>
-      <c r="D10" s="140" t="s">
+      <c r="C10" s="128"/>
+      <c r="D10" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="141" t="s">
+      <c r="E10" s="130" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" s="146" t="s">
+      <c r="A11" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="147" t="s">
+      <c r="B11" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="148"/>
-      <c r="D11" s="149" t="s">
+      <c r="C11" s="135"/>
+      <c r="D11" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="150" t="s">
+      <c r="E11" s="132" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" ht="17.6" spans="1:20">
-      <c r="A13" s="131" t="s">
+      <c r="A13" s="120" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="131"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="131"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="131"/>
-      <c r="M13" s="131"/>
-      <c r="N13" s="131"/>
-      <c r="O13" s="131"/>
-      <c r="P13" s="131"/>
-      <c r="Q13" s="131"/>
-      <c r="R13" s="131"/>
-      <c r="S13" s="131"/>
-      <c r="T13" s="131"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="120"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="120"/>
+      <c r="I13" s="120"/>
+      <c r="J13" s="120"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="120"/>
+      <c r="Q13" s="120"/>
+      <c r="R13" s="120"/>
+      <c r="S13" s="120"/>
+      <c r="T13" s="120"/>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="151" t="s">
+      <c r="A14" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="152"/>
-      <c r="C14" s="153"/>
-      <c r="D14" s="154" t="s">
+      <c r="B14" s="138"/>
+      <c r="C14" s="139"/>
+      <c r="D14" s="140" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="155"/>
-      <c r="F14" s="156"/>
-      <c r="G14" s="157" t="s">
+      <c r="E14" s="141"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="143" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="158"/>
-      <c r="I14" s="159"/>
-      <c r="J14" s="157" t="s">
+      <c r="H14" s="144"/>
+      <c r="I14" s="145"/>
+      <c r="J14" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="K14" s="158"/>
-      <c r="L14" s="159"/>
-      <c r="M14" s="160" t="s">
+      <c r="K14" s="144"/>
+      <c r="L14" s="145"/>
+      <c r="M14" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="N14" s="161"/>
-      <c r="O14" s="162"/>
-      <c r="P14" s="163" t="s">
+      <c r="N14" s="147"/>
+      <c r="O14" s="148"/>
+      <c r="P14" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="164"/>
-      <c r="R14" s="165"/>
-      <c r="S14" s="154" t="s">
+      <c r="Q14" s="150"/>
+      <c r="R14" s="151"/>
+      <c r="S14" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="T14" s="156"/>
+      <c r="T14" s="142"/>
     </row>
     <row r="15" ht="26" spans="1:20">
-      <c r="A15" s="166">
+      <c r="A15" s="152">
         <f>COUNTA($B$47:$B$60)</f>
         <v>14</v>
       </c>
-      <c r="B15" s="167"/>
-      <c r="C15" s="168"/>
-      <c r="D15" s="169">
+      <c r="B15" s="153"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="155">
         <f>COUNTIF($E$47:$E$60,"Core complete / stabilize")+COUNTIF($E$47:$E$60,"Core complete / optimize")</f>
         <v>3</v>
       </c>
-      <c r="E15" s="170"/>
-      <c r="F15" s="171"/>
-      <c r="G15" s="172">
+      <c r="E15" s="156"/>
+      <c r="F15" s="157"/>
+      <c r="G15" s="158">
         <f>COUNTIF($E$47:$E$60,"Core complete / stabilize")+COUNTIF($E$47:$E$60,"Core complete / optimize")</f>
         <v>3</v>
       </c>
-      <c r="H15" s="173"/>
-      <c r="I15" s="174"/>
-      <c r="J15" s="172">
+      <c r="H15" s="159"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="158">
         <f>COUNTIF($E$47:$E$60,"Pending")+COUNTIF($E$47:$E$60,"Planned")</f>
         <v>9</v>
       </c>
-      <c r="K15" s="173"/>
-      <c r="L15" s="174"/>
-      <c r="M15" s="175">
+      <c r="K15" s="159"/>
+      <c r="L15" s="160"/>
+      <c r="M15" s="161">
         <f>COUNTIF($E$47:$E$60,"Deferred")</f>
         <v>1</v>
       </c>
-      <c r="N15" s="176"/>
-      <c r="O15" s="177"/>
-      <c r="P15" s="178">
+      <c r="N15" s="162"/>
+      <c r="O15" s="163"/>
+      <c r="P15" s="164">
         <f>COUNTIF($E$47:$E$60,"Dropped")</f>
         <v>1</v>
       </c>
-      <c r="Q15" s="179"/>
-      <c r="R15" s="180"/>
-      <c r="S15" s="169">
+      <c r="Q15" s="165"/>
+      <c r="R15" s="166"/>
+      <c r="S15" s="155">
         <f>COUNTIF($F$47:$F$60,"Handoff")</f>
         <v>4</v>
       </c>
-      <c r="T15" s="171"/>
+      <c r="T15" s="157"/>
     </row>
     <row r="18" ht="17.6" spans="1:20">
-      <c r="A18" s="181" t="s">
+      <c r="A18" s="167" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="181"/>
-      <c r="C18" s="181"/>
-      <c r="D18" s="181"/>
-      <c r="E18" s="181"/>
-      <c r="F18" s="181"/>
-      <c r="G18" s="181"/>
-      <c r="H18" s="181"/>
-      <c r="I18" s="181"/>
-      <c r="J18" s="181"/>
-      <c r="K18" s="181"/>
-      <c r="L18" s="181"/>
-      <c r="M18" s="181"/>
-      <c r="N18" s="181"/>
-      <c r="O18" s="181"/>
-      <c r="P18" s="181"/>
-      <c r="Q18" s="181"/>
-      <c r="R18" s="181"/>
-      <c r="S18" s="181"/>
-      <c r="T18" s="181"/>
+      <c r="B18" s="167"/>
+      <c r="C18" s="167"/>
+      <c r="D18" s="167"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="167"/>
+      <c r="H18" s="167"/>
+      <c r="I18" s="167"/>
+      <c r="J18" s="167"/>
+      <c r="K18" s="167"/>
+      <c r="L18" s="167"/>
+      <c r="M18" s="167"/>
+      <c r="N18" s="167"/>
+      <c r="O18" s="167"/>
+      <c r="P18" s="167"/>
+      <c r="Q18" s="167"/>
+      <c r="R18" s="167"/>
+      <c r="S18" s="167"/>
+      <c r="T18" s="167"/>
     </row>
     <row r="19" ht="17.55" spans="1:20">
-      <c r="A19" s="182"/>
-      <c r="B19" s="182"/>
-      <c r="C19" s="182"/>
-      <c r="D19" s="182"/>
-      <c r="E19" s="182"/>
-      <c r="F19" s="182"/>
+      <c r="A19" s="168"/>
+      <c r="B19" s="168"/>
+      <c r="C19" s="168"/>
+      <c r="D19" s="168"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="168"/>
     </row>
     <row r="20" ht="17.55" spans="1:20">
-      <c r="A20" s="183" t="s">
+      <c r="A20" s="169" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="184" t="s">
+      <c r="B20" s="170" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="184" t="s">
+      <c r="C20" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="184" t="s">
+      <c r="D20" s="170" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="184" t="s">
+      <c r="E20" s="170" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="185" t="s">
+      <c r="F20" s="171" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="21" ht="41" spans="1:20">
-      <c r="A21" s="186" t="s">
+      <c r="A21" s="172" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="133" t="s">
+      <c r="B21" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="133" t="s">
+      <c r="C21" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="187" t="s">
+      <c r="D21" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="187" t="s">
+      <c r="E21" s="173" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="188" t="s">
+      <c r="F21" s="174" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" ht="28" spans="1:20">
-      <c r="A22" s="189" t="s">
+      <c r="A22" s="175" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="138" t="s">
+      <c r="B22" s="127" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="138" t="s">
+      <c r="C22" s="127" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="190" t="s">
+      <c r="D22" s="176" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="190" t="s">
+      <c r="E22" s="176" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="191" t="s">
+      <c r="F22" s="177" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:20">
-      <c r="A23" s="189" t="s">
+      <c r="A23" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="138" t="s">
+      <c r="B23" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="138" t="s">
+      <c r="C23" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="D23" s="190" t="s">
+      <c r="D23" s="176" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="190" t="s">
+      <c r="E23" s="176" t="s">
         <v>59</v>
       </c>
-      <c r="F23" s="191" t="s">
+      <c r="F23" s="177" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" ht="28" spans="1:20">
-      <c r="A24" s="189" t="s">
+      <c r="A24" s="175" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="138" t="s">
+      <c r="B24" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="138" t="s">
+      <c r="C24" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="190" t="s">
+      <c r="D24" s="176" t="s">
         <v>63</v>
       </c>
-      <c r="E24" s="190" t="s">
+      <c r="E24" s="176" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="191" t="s">
+      <c r="F24" s="177" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="25" ht="28.75" spans="1:20">
-      <c r="A25" s="192" t="s">
+      <c r="A25" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="193" t="s">
+      <c r="B25" s="179" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="193" t="s">
+      <c r="C25" s="179" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="194" t="s">
+      <c r="D25" s="180" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="194" t="s">
+      <c r="E25" s="180" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="195" t="s">
+      <c r="F25" s="181" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="28" ht="17.6" spans="1:20">
-      <c r="A28" s="196" t="s">
+      <c r="A28" s="182" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="196"/>
-      <c r="C28" s="196"/>
-      <c r="D28" s="196"/>
-      <c r="E28" s="196"/>
-      <c r="F28" s="196"/>
-      <c r="G28" s="196"/>
-      <c r="H28" s="196"/>
-      <c r="I28" s="196"/>
-      <c r="J28" s="196"/>
-      <c r="K28" s="196"/>
-      <c r="L28" s="196"/>
-      <c r="M28" s="196"/>
-      <c r="N28" s="196"/>
-      <c r="O28" s="196"/>
-      <c r="P28" s="196"/>
-      <c r="Q28" s="196"/>
-      <c r="R28" s="196"/>
-      <c r="S28" s="196"/>
-      <c r="T28" s="196"/>
+      <c r="B28" s="182"/>
+      <c r="C28" s="182"/>
+      <c r="D28" s="182"/>
+      <c r="E28" s="182"/>
+      <c r="F28" s="182"/>
+      <c r="G28" s="182"/>
+      <c r="H28" s="182"/>
+      <c r="I28" s="182"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="182"/>
+      <c r="L28" s="182"/>
+      <c r="M28" s="182"/>
+      <c r="N28" s="182"/>
+      <c r="O28" s="182"/>
+      <c r="P28" s="182"/>
+      <c r="Q28" s="182"/>
+      <c r="R28" s="182"/>
+      <c r="S28" s="182"/>
+      <c r="T28" s="182"/>
     </row>
     <row r="29" spans="1:20">
-      <c r="A29" s="182"/>
-      <c r="B29" s="182"/>
-      <c r="C29" s="182"/>
-      <c r="D29" s="182"/>
-      <c r="E29" s="182"/>
-      <c r="F29" s="182"/>
-      <c r="G29" s="182"/>
-      <c r="H29" s="182"/>
-      <c r="I29" s="182"/>
+      <c r="A29" s="168"/>
+      <c r="B29" s="168"/>
+      <c r="C29" s="168"/>
+      <c r="D29" s="168"/>
+      <c r="E29" s="168"/>
+      <c r="F29" s="168"/>
+      <c r="G29" s="168"/>
+      <c r="H29" s="168"/>
+      <c r="I29" s="168"/>
     </row>
     <row r="30" spans="1:20">
-      <c r="A30" s="197" t="s">
+      <c r="A30" s="183" t="s">
         <v>70</v>
       </c>
-      <c r="B30" s="198" t="s">
+      <c r="B30" s="184" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="198" t="s">
+      <c r="C30" s="184" t="s">
         <v>72</v>
       </c>
-      <c r="D30" s="198" t="s">
+      <c r="D30" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="198" t="s">
+      <c r="E30" s="184" t="s">
         <v>74</v>
       </c>
-      <c r="F30" s="198" t="s">
+      <c r="F30" s="184" t="s">
         <v>75</v>
       </c>
-      <c r="G30" s="198" t="s">
+      <c r="G30" s="184" t="s">
         <v>76</v>
       </c>
-      <c r="H30" s="198" t="s">
+      <c r="H30" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="I30" s="199" t="s">
+      <c r="I30" s="185" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="31" ht="28" spans="1:20">
-      <c r="A31" s="200">
+      <c r="A31" s="186">
         <v>1</v>
       </c>
-      <c r="B31" s="133" t="s">
+      <c r="B31" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="133" t="s">
+      <c r="C31" s="122" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="133" t="s">
+      <c r="D31" s="122" t="s">
         <v>81</v>
       </c>
-      <c r="E31" s="133" t="s">
+      <c r="E31" s="122" t="s">
         <v>82</v>
       </c>
-      <c r="F31" s="133" t="s">
+      <c r="F31" s="122" t="s">
         <v>83</v>
       </c>
-      <c r="G31" s="133" t="s">
+      <c r="G31" s="122" t="s">
         <v>84</v>
       </c>
-      <c r="H31" s="133" t="s">
+      <c r="H31" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="I31" s="201" t="s">
+      <c r="I31" s="187" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="32" ht="28" spans="1:20">
-      <c r="A32" s="202">
+      <c r="A32" s="188">
         <v>2</v>
       </c>
-      <c r="B32" s="138" t="s">
+      <c r="B32" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="138" t="s">
+      <c r="C32" s="127" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="138" t="s">
+      <c r="D32" s="127" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="138" t="s">
+      <c r="E32" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="F32" s="138" t="s">
+      <c r="F32" s="127" t="s">
         <v>90</v>
       </c>
-      <c r="G32" s="138" t="s">
+      <c r="G32" s="127" t="s">
         <v>91</v>
       </c>
-      <c r="H32" s="138" t="s">
+      <c r="H32" s="127" t="s">
         <v>85</v>
       </c>
-      <c r="I32" s="203" t="s">
+      <c r="I32" s="189" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="33" ht="28" spans="1:23">
-      <c r="A33" s="202">
+      <c r="A33" s="188">
         <v>3</v>
       </c>
-      <c r="B33" s="138" t="s">
+      <c r="B33" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="138" t="s">
+      <c r="C33" s="127" t="s">
         <v>93</v>
       </c>
-      <c r="D33" s="138" t="s">
+      <c r="D33" s="127" t="s">
         <v>94</v>
       </c>
-      <c r="E33" s="138" t="s">
+      <c r="E33" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="F33" s="138" t="s">
+      <c r="F33" s="127" t="s">
         <v>90</v>
       </c>
-      <c r="G33" s="138" t="s">
+      <c r="G33" s="127" t="s">
         <v>95</v>
       </c>
-      <c r="H33" s="138" t="s">
+      <c r="H33" s="127" t="s">
         <v>96</v>
       </c>
-      <c r="I33" s="203" t="s">
+      <c r="I33" s="189" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="34" ht="28" spans="1:23">
-      <c r="A34" s="202">
+      <c r="A34" s="188">
         <v>4</v>
       </c>
-      <c r="B34" s="138" t="s">
+      <c r="B34" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="138" t="s">
+      <c r="C34" s="127" t="s">
         <v>98</v>
       </c>
-      <c r="D34" s="138" t="s">
+      <c r="D34" s="127" t="s">
         <v>99</v>
       </c>
-      <c r="E34" s="138" t="s">
+      <c r="E34" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="F34" s="138" t="s">
+      <c r="F34" s="127" t="s">
         <v>100</v>
       </c>
-      <c r="G34" s="138" t="s">
+      <c r="G34" s="127" t="s">
         <v>101</v>
       </c>
-      <c r="H34" s="138" t="s">
+      <c r="H34" s="127" t="s">
         <v>102</v>
       </c>
-      <c r="I34" s="203" t="s">
+      <c r="I34" s="189" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="35" ht="28" spans="1:23">
-      <c r="A35" s="202">
+      <c r="A35" s="188">
         <v>5</v>
       </c>
-      <c r="B35" s="138" t="s">
+      <c r="B35" s="127" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="138" t="s">
+      <c r="C35" s="127" t="s">
         <v>105</v>
       </c>
-      <c r="D35" s="138" t="s">
+      <c r="D35" s="127" t="s">
         <v>106</v>
       </c>
-      <c r="E35" s="138" t="s">
+      <c r="E35" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="F35" s="138" t="s">
+      <c r="F35" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="G35" s="138" t="s">
+      <c r="G35" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="H35" s="138" t="s">
+      <c r="H35" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="I35" s="203" t="s">
+      <c r="I35" s="189" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="36" ht="28" spans="1:23">
-      <c r="A36" s="202">
+      <c r="A36" s="188">
         <v>6</v>
       </c>
-      <c r="B36" s="138" t="s">
+      <c r="B36" s="127" t="s">
         <v>104</v>
       </c>
-      <c r="C36" s="138" t="s">
+      <c r="C36" s="127" t="s">
         <v>112</v>
       </c>
-      <c r="D36" s="138" t="s">
+      <c r="D36" s="127" t="s">
         <v>113</v>
       </c>
-      <c r="E36" s="138" t="s">
+      <c r="E36" s="127" t="s">
         <v>114</v>
       </c>
-      <c r="F36" s="138" t="s">
+      <c r="F36" s="127" t="s">
         <v>115</v>
       </c>
-      <c r="G36" s="138" t="s">
+      <c r="G36" s="127" t="s">
         <v>116</v>
       </c>
-      <c r="H36" s="138" t="s">
+      <c r="H36" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="I36" s="203" t="s">
+      <c r="I36" s="189" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="37" ht="28" spans="1:23">
-      <c r="A37" s="202">
+      <c r="A37" s="188">
         <v>7</v>
       </c>
-      <c r="B37" s="138" t="s">
+      <c r="B37" s="127" t="s">
         <v>117</v>
       </c>
-      <c r="C37" s="138" t="s">
+      <c r="C37" s="127" t="s">
         <v>118</v>
       </c>
-      <c r="D37" s="138" t="s">
+      <c r="D37" s="127" t="s">
         <v>119</v>
       </c>
-      <c r="E37" s="138" t="s">
+      <c r="E37" s="127" t="s">
         <v>120</v>
       </c>
-      <c r="F37" s="138" t="s">
+      <c r="F37" s="127" t="s">
         <v>121</v>
       </c>
-      <c r="G37" s="138" t="s">
+      <c r="G37" s="127" t="s">
         <v>122</v>
       </c>
-      <c r="H37" s="138" t="s">
+      <c r="H37" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="I37" s="203" t="s">
+      <c r="I37" s="189" t="s">
         <v>124</v>
       </c>
-      <c r="V37" s="204" t="s">
+      <c r="V37" s="190" t="s">
         <v>125</v>
       </c>
-      <c r="W37" s="204" t="s">
+      <c r="W37" s="190" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="38" ht="28" spans="1:23">
-      <c r="A38" s="202">
+      <c r="A38" s="188">
         <v>8</v>
       </c>
-      <c r="B38" s="138" t="s">
+      <c r="B38" s="127" t="s">
         <v>127</v>
       </c>
-      <c r="C38" s="138" t="s">
+      <c r="C38" s="127" t="s">
         <v>128</v>
       </c>
-      <c r="D38" s="138" t="s">
+      <c r="D38" s="127" t="s">
         <v>129</v>
       </c>
-      <c r="E38" s="138" t="s">
+      <c r="E38" s="127" t="s">
         <v>120</v>
       </c>
-      <c r="F38" s="138" t="s">
+      <c r="F38" s="127" t="s">
         <v>130</v>
       </c>
-      <c r="G38" s="138" t="s">
+      <c r="G38" s="127" t="s">
         <v>131</v>
       </c>
-      <c r="H38" s="138" t="s">
+      <c r="H38" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="I38" s="203" t="s">
+      <c r="I38" s="189" t="s">
         <v>132</v>
       </c>
-      <c r="V38" s="205" t="s">
+      <c r="V38" s="191" t="s">
         <v>133</v>
       </c>
-      <c r="W38" s="205">
+      <c r="W38" s="191">
         <f>COUNTIF($E$47:$E$60,V38)</f>
         <v>2</v>
       </c>
     </row>
     <row r="39" ht="28" spans="1:23">
-      <c r="A39" s="202">
+      <c r="A39" s="188">
         <v>9</v>
       </c>
-      <c r="B39" s="138" t="s">
+      <c r="B39" s="127" t="s">
         <v>134</v>
       </c>
-      <c r="C39" s="138" t="s">
+      <c r="C39" s="127" t="s">
         <v>135</v>
       </c>
-      <c r="D39" s="138" t="s">
+      <c r="D39" s="127" t="s">
         <v>136</v>
       </c>
-      <c r="E39" s="138" t="s">
+      <c r="E39" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="F39" s="138" t="s">
+      <c r="F39" s="127" t="s">
         <v>137</v>
       </c>
-      <c r="G39" s="138" t="s">
+      <c r="G39" s="127" t="s">
         <v>138</v>
       </c>
-      <c r="H39" s="138" t="s">
+      <c r="H39" s="127" t="s">
         <v>139</v>
       </c>
-      <c r="I39" s="203" t="s">
+      <c r="I39" s="189" t="s">
         <v>140</v>
       </c>
-      <c r="V39" s="205" t="s">
+      <c r="V39" s="191" t="s">
         <v>141</v>
       </c>
-      <c r="W39" s="205">
+      <c r="W39" s="191">
         <f>COUNTIF($E$47:$E$60,V39)</f>
         <v>1</v>
       </c>
     </row>
     <row r="40" ht="28" spans="1:23">
-      <c r="A40" s="202">
+      <c r="A40" s="188">
         <v>10</v>
       </c>
-      <c r="B40" s="138" t="s">
+      <c r="B40" s="127" t="s">
         <v>142</v>
       </c>
-      <c r="C40" s="138" t="s">
+      <c r="C40" s="127" t="s">
         <v>143</v>
       </c>
-      <c r="D40" s="138" t="s">
+      <c r="D40" s="127" t="s">
         <v>144</v>
       </c>
-      <c r="E40" s="138" t="s">
+      <c r="E40" s="127" t="s">
         <v>145</v>
       </c>
-      <c r="F40" s="138" t="s">
+      <c r="F40" s="127" t="s">
         <v>146</v>
       </c>
-      <c r="G40" s="138" t="s">
+      <c r="G40" s="127" t="s">
         <v>147</v>
       </c>
-      <c r="H40" s="138" t="s">
+      <c r="H40" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="I40" s="203" t="s">
+      <c r="I40" s="189" t="s">
         <v>148</v>
       </c>
-      <c r="V40" s="205" t="s">
+      <c r="V40" s="191" t="s">
         <v>149</v>
       </c>
-      <c r="W40" s="205">
+      <c r="W40" s="191">
         <f>COUNTIF($E$47:$E$60,V40)</f>
         <v>8</v>
       </c>
     </row>
     <row r="41" ht="28" spans="1:23">
-      <c r="A41" s="202">
+      <c r="A41" s="188">
         <v>11</v>
       </c>
-      <c r="B41" s="138" t="s">
+      <c r="B41" s="127" t="s">
         <v>150</v>
       </c>
-      <c r="C41" s="138" t="s">
+      <c r="C41" s="127" t="s">
         <v>151</v>
       </c>
-      <c r="D41" s="138" t="s">
+      <c r="D41" s="127" t="s">
         <v>152</v>
       </c>
-      <c r="E41" s="138" t="s">
+      <c r="E41" s="127" t="s">
         <v>153</v>
       </c>
-      <c r="F41" s="138" t="s">
+      <c r="F41" s="127" t="s">
         <v>154</v>
       </c>
-      <c r="G41" s="138" t="s">
+      <c r="G41" s="127" t="s">
         <v>155</v>
       </c>
-      <c r="H41" s="138" t="s">
+      <c r="H41" s="127" t="s">
         <v>156</v>
       </c>
-      <c r="I41" s="203" t="s">
+      <c r="I41" s="189" t="s">
         <v>157</v>
       </c>
-      <c r="V41" s="205" t="s">
+      <c r="V41" s="191" t="s">
         <v>158</v>
       </c>
-      <c r="W41" s="205">
+      <c r="W41" s="191">
         <f>COUNTIF($E$47:$E$60,V41)</f>
         <v>1</v>
       </c>
     </row>
     <row r="42" ht="28" spans="1:23">
-      <c r="A42" s="202">
+      <c r="A42" s="188">
         <v>12</v>
       </c>
-      <c r="B42" s="138" t="s">
+      <c r="B42" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="C42" s="138" t="s">
+      <c r="C42" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="D42" s="138" t="s">
+      <c r="D42" s="127" t="s">
         <v>161</v>
       </c>
-      <c r="E42" s="138" t="s">
+      <c r="E42" s="127" t="s">
         <v>162</v>
       </c>
-      <c r="F42" s="138" t="s">
+      <c r="F42" s="127" t="s">
         <v>163</v>
       </c>
-      <c r="G42" s="138" t="s">
+      <c r="G42" s="127" t="s">
         <v>164</v>
       </c>
-      <c r="H42" s="138" t="s">
+      <c r="H42" s="127" t="s">
         <v>165</v>
       </c>
-      <c r="I42" s="203" t="s">
+      <c r="I42" s="189" t="s">
         <v>166</v>
       </c>
-      <c r="V42" s="205" t="s">
+      <c r="V42" s="191" t="s">
         <v>12</v>
       </c>
-      <c r="W42" s="205">
+      <c r="W42" s="191">
         <f>COUNTIF($E$47:$E$60,V42)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="43" s="127" customFormat="1" ht="17.6" spans="1:23">
-      <c r="A43" s="206"/>
-      <c r="B43" s="207"/>
-      <c r="C43" s="207"/>
-      <c r="D43" s="207"/>
-      <c r="E43" s="207"/>
-      <c r="F43" s="207"/>
-      <c r="G43" s="207"/>
-      <c r="H43" s="207"/>
-      <c r="I43" s="208"/>
-      <c r="J43" s="209"/>
-      <c r="K43" s="209"/>
-      <c r="L43" s="209"/>
-      <c r="M43" s="209"/>
-      <c r="N43" s="209"/>
-      <c r="O43" s="209"/>
-      <c r="P43" s="209"/>
-      <c r="Q43" s="209"/>
-      <c r="R43" s="209"/>
-      <c r="S43" s="209"/>
-      <c r="T43" s="209"/>
-      <c r="V43" s="210"/>
-      <c r="W43" s="210"/>
+    <row r="43" s="116" customFormat="1" ht="17.6" spans="1:23">
+      <c r="A43" s="192"/>
+      <c r="B43" s="192"/>
+      <c r="C43" s="192"/>
+      <c r="D43" s="192"/>
+      <c r="E43" s="192"/>
+      <c r="F43" s="192"/>
+      <c r="G43" s="192"/>
+      <c r="H43" s="192"/>
+      <c r="I43" s="192"/>
+      <c r="J43" s="193"/>
+      <c r="K43" s="193"/>
+      <c r="L43" s="193"/>
+      <c r="M43" s="193"/>
+      <c r="N43" s="193"/>
+      <c r="O43" s="193"/>
+      <c r="P43" s="193"/>
+      <c r="Q43" s="193"/>
+      <c r="R43" s="193"/>
+      <c r="S43" s="193"/>
+      <c r="T43" s="193"/>
+      <c r="V43" s="194"/>
+      <c r="W43" s="194"/>
     </row>
     <row r="44" ht="17.6" spans="1:23">
-      <c r="A44" s="211" t="s">
+      <c r="A44" s="195" t="s">
         <v>167</v>
       </c>
-      <c r="B44" s="212" t="s">
+      <c r="B44" s="196" t="s">
         <v>127</v>
       </c>
-      <c r="C44" s="212" t="s">
+      <c r="C44" s="196" t="s">
         <v>168</v>
       </c>
-      <c r="D44" s="212" t="s">
+      <c r="D44" s="196" t="s">
         <v>169</v>
       </c>
-      <c r="E44" s="212" t="s">
+      <c r="E44" s="196" t="s">
         <v>170</v>
       </c>
-      <c r="F44" s="212" t="s">
+      <c r="F44" s="196" t="s">
         <v>171</v>
       </c>
-      <c r="G44" s="212" t="s">
+      <c r="G44" s="196" t="s">
         <v>172</v>
       </c>
-      <c r="H44" s="212" t="s">
+      <c r="H44" s="196" t="s">
         <v>173</v>
       </c>
-      <c r="I44" s="213" t="s">
+      <c r="I44" s="197" t="s">
         <v>174</v>
       </c>
-      <c r="J44" s="214"/>
-      <c r="K44" s="214"/>
-      <c r="L44" s="214"/>
-      <c r="M44" s="214"/>
-      <c r="N44" s="214"/>
-      <c r="O44" s="214"/>
-      <c r="P44" s="214"/>
-      <c r="Q44" s="214"/>
-      <c r="R44" s="214"/>
-      <c r="S44" s="214"/>
-      <c r="T44" s="214"/>
-      <c r="V44" s="205" t="s">
+      <c r="J44" s="198"/>
+      <c r="K44" s="198"/>
+      <c r="L44" s="198"/>
+      <c r="M44" s="198"/>
+      <c r="N44" s="198"/>
+      <c r="O44" s="198"/>
+      <c r="P44" s="198"/>
+      <c r="Q44" s="198"/>
+      <c r="R44" s="198"/>
+      <c r="S44" s="198"/>
+      <c r="T44" s="198"/>
+      <c r="V44" s="191" t="s">
         <v>16</v>
       </c>
-      <c r="W44" s="205">
+      <c r="W44" s="191">
         <f>COUNTIF($E$47:$E$60,V44)</f>
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:23">
-      <c r="A45" s="215"/>
-      <c r="B45" s="216"/>
-      <c r="C45" s="216"/>
-      <c r="D45" s="216"/>
-      <c r="E45" s="216"/>
-      <c r="F45" s="216"/>
-      <c r="G45" s="216"/>
-      <c r="H45" s="216"/>
-      <c r="I45" s="217"/>
-      <c r="J45" s="182"/>
-      <c r="K45" s="182"/>
-      <c r="L45" s="182"/>
-      <c r="M45" s="182"/>
-      <c r="N45" s="182"/>
-      <c r="O45" s="182"/>
-      <c r="P45" s="182"/>
-      <c r="Q45" s="182"/>
-      <c r="R45" s="182"/>
-      <c r="S45" s="182"/>
-      <c r="T45" s="182"/>
+      <c r="A45" s="199"/>
+      <c r="B45" s="200"/>
+      <c r="C45" s="200"/>
+      <c r="D45" s="200"/>
+      <c r="E45" s="200"/>
+      <c r="F45" s="200"/>
+      <c r="G45" s="200"/>
+      <c r="H45" s="200"/>
+      <c r="I45" s="201"/>
+      <c r="J45" s="168"/>
+      <c r="K45" s="168"/>
+      <c r="L45" s="168"/>
+      <c r="M45" s="168"/>
+      <c r="N45" s="168"/>
+      <c r="O45" s="168"/>
+      <c r="P45" s="168"/>
+      <c r="Q45" s="168"/>
+      <c r="R45" s="168"/>
+      <c r="S45" s="168"/>
+      <c r="T45" s="168"/>
     </row>
     <row r="46" spans="1:23">
-      <c r="A46" s="218" t="s">
+      <c r="A46" s="202" t="s">
         <v>70</v>
       </c>
-      <c r="B46" s="218" t="s">
+      <c r="B46" s="202" t="s">
         <v>175</v>
       </c>
-      <c r="C46" s="218" t="s">
+      <c r="C46" s="202" t="s">
         <v>176</v>
       </c>
-      <c r="D46" s="218" t="s">
+      <c r="D46" s="202" t="s">
         <v>177</v>
       </c>
-      <c r="E46" s="218" t="s">
+      <c r="E46" s="202" t="s">
         <v>125</v>
       </c>
-      <c r="F46" s="218" t="s">
+      <c r="F46" s="202" t="s">
         <v>178</v>
       </c>
-      <c r="G46" s="218" t="s">
+      <c r="G46" s="202" t="s">
         <v>179</v>
       </c>
-      <c r="H46" s="218" t="s">
+      <c r="H46" s="202" t="s">
         <v>180</v>
       </c>
-      <c r="I46" s="218" t="s">
+      <c r="I46" s="202" t="s">
         <v>181</v>
       </c>
-      <c r="J46" s="218" t="s">
+      <c r="J46" s="202" t="s">
         <v>182</v>
       </c>
-      <c r="K46" s="218" t="s">
+      <c r="K46" s="202" t="s">
         <v>183</v>
       </c>
-      <c r="L46" s="218" t="s">
+      <c r="L46" s="202" t="s">
         <v>184</v>
       </c>
-      <c r="M46" s="218" t="s">
+      <c r="M46" s="202" t="s">
         <v>185</v>
       </c>
-      <c r="N46" s="218" t="s">
+      <c r="N46" s="202" t="s">
         <v>186</v>
       </c>
-      <c r="O46" s="218" t="s">
+      <c r="O46" s="202" t="s">
         <v>187</v>
       </c>
-      <c r="P46" s="218" t="s">
+      <c r="P46" s="202" t="s">
         <v>188</v>
       </c>
-      <c r="Q46" s="218" t="s">
+      <c r="Q46" s="202" t="s">
         <v>189</v>
       </c>
-      <c r="R46" s="218" t="s">
+      <c r="R46" s="202" t="s">
         <v>190</v>
       </c>
-      <c r="S46" s="218" t="s">
+      <c r="S46" s="202" t="s">
         <v>191</v>
       </c>
-      <c r="T46" s="218" t="s">
+      <c r="T46" s="202" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="47" ht="41" spans="1:23">
-      <c r="A47" s="219">
+      <c r="A47" s="203">
         <v>1</v>
       </c>
-      <c r="B47" s="138" t="s">
+      <c r="B47" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="C47" s="138" t="s">
+      <c r="C47" s="127" t="s">
         <v>193</v>
       </c>
-      <c r="D47" s="138" t="s">
+      <c r="D47" s="127" t="s">
         <v>194</v>
       </c>
-      <c r="E47" s="138" t="s">
+      <c r="E47" s="127" t="s">
         <v>133</v>
       </c>
-      <c r="F47" s="138" t="s">
+      <c r="F47" s="127" t="s">
         <v>195</v>
       </c>
-      <c r="G47" s="190" t="s">
+      <c r="G47" s="176" t="s">
         <v>196</v>
       </c>
-      <c r="H47" s="138" t="str">
+      <c r="H47" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/AI-VIDEO-CREATIVE-WORKFLOWS/AI-VIDEO-CREATIVE-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I47" s="138" t="str">
+      <c r="I47" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bai-ugc-short-video%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J47" s="220">
+      <c r="J47" s="204">
         <v>46237</v>
       </c>
-      <c r="K47" s="220" t="s">
+      <c r="K47" s="204" t="s">
         <v>197</v>
       </c>
-      <c r="L47" s="138" t="str">
+      <c r="L47" s="127" t="str">
         <f>HYPERLINK("#'AI UGC Video'!A1","Mở chi tiết")</f>
         <v>Mở chi tiết</v>
       </c>
-      <c r="M47" s="138" t="s">
+      <c r="M47" s="127" t="s">
         <v>198</v>
       </c>
-      <c r="N47" s="138" t="s">
+      <c r="N47" s="127" t="s">
         <v>199</v>
       </c>
-      <c r="O47" s="138" t="s">
+      <c r="O47" s="127" t="s">
         <v>200</v>
       </c>
-      <c r="P47" s="138" t="s">
+      <c r="P47" s="127" t="s">
         <v>201</v>
       </c>
-      <c r="Q47" s="138" t="s">
+      <c r="Q47" s="127" t="s">
         <v>202</v>
       </c>
-      <c r="R47" s="138" t="s">
+      <c r="R47" s="127" t="s">
         <v>203</v>
       </c>
-      <c r="S47" s="138" t="s">
+      <c r="S47" s="127" t="s">
         <v>204</v>
       </c>
-      <c r="T47" s="138" t="s">
+      <c r="T47" s="127" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="48" ht="55" spans="1:23">
-      <c r="A48" s="219">
+      <c r="A48" s="203">
         <v>2</v>
       </c>
-      <c r="B48" s="138" t="s">
+      <c r="B48" s="127" t="s">
         <v>55</v>
       </c>
-      <c r="C48" s="138" t="s">
+      <c r="C48" s="127" t="s">
         <v>206</v>
       </c>
-      <c r="D48" s="138" t="s">
+      <c r="D48" s="127" t="s">
         <v>207</v>
       </c>
-      <c r="E48" s="138" t="s">
+      <c r="E48" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="F48" s="138" t="s">
+      <c r="F48" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="190" t="s">
+      <c r="G48" s="176" t="s">
         <v>208</v>
       </c>
-      <c r="H48" s="138" t="str">
+      <c r="H48" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/AI-VIDEO-CREATIVE-WORKFLOWS/AI-VIDEO-CREATIVE-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I48" s="138" t="str">
+      <c r="I48" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bai-clone-short-video%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J48" s="220">
+      <c r="J48" s="204">
         <v>46246</v>
       </c>
-      <c r="K48" s="220"/>
-      <c r="L48" s="138" t="str">
+      <c r="K48" s="204"/>
+      <c r="L48" s="127" t="str">
         <f>HYPERLINK("#'AI Clone Video'!A1","Mở chi tiết")</f>
         <v>Mở chi tiết</v>
       </c>
-      <c r="M48" s="138" t="s">
+      <c r="M48" s="127" t="s">
         <v>209</v>
       </c>
-      <c r="N48" s="138" t="s">
+      <c r="N48" s="127" t="s">
         <v>210</v>
       </c>
-      <c r="O48" s="138" t="s">
+      <c r="O48" s="127" t="s">
         <v>211</v>
       </c>
-      <c r="P48" s="138" t="s">
+      <c r="P48" s="127" t="s">
         <v>212</v>
       </c>
-      <c r="Q48" s="138" t="s">
+      <c r="Q48" s="127" t="s">
         <v>213</v>
       </c>
-      <c r="R48" s="138" t="s">
+      <c r="R48" s="127" t="s">
         <v>214</v>
       </c>
-      <c r="S48" s="138" t="s">
+      <c r="S48" s="127" t="s">
         <v>215</v>
       </c>
-      <c r="T48" s="138" t="s">
+      <c r="T48" s="127" t="s">
         <v>216</v>
       </c>
-      <c r="V48" s="204" t="s">
+      <c r="V48" s="190" t="s">
         <v>217</v>
       </c>
-      <c r="W48" s="204" t="s">
+      <c r="W48" s="190" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="49" ht="41" spans="1:23">
-      <c r="A49" s="219">
+      <c r="A49" s="203">
         <v>3</v>
       </c>
-      <c r="B49" s="138" t="s">
+      <c r="B49" s="127" t="s">
         <v>218</v>
       </c>
-      <c r="C49" s="138" t="s">
+      <c r="C49" s="127" t="s">
         <v>219</v>
       </c>
-      <c r="D49" s="138" t="s">
+      <c r="D49" s="127" t="s">
         <v>220</v>
       </c>
-      <c r="E49" s="138" t="s">
+      <c r="E49" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="F49" s="138" t="s">
+      <c r="F49" s="127" t="s">
         <v>221</v>
       </c>
-      <c r="G49" s="190" t="s">
+      <c r="G49" s="176" t="s">
         <v>222</v>
       </c>
-      <c r="H49" s="138" t="str">
+      <c r="H49" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/AI-VIDEO-CREATIVE-WORKFLOWS/AI-VIDEO-CREATIVE-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I49" s="138" t="str">
+      <c r="I49" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bai-commercial-short-video%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J49" s="220">
+      <c r="J49" s="204">
         <v>46237</v>
       </c>
-      <c r="K49" s="220"/>
-      <c r="L49" s="138" t="s">
+      <c r="K49" s="204"/>
+      <c r="L49" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="M49" s="138" t="s">
+      <c r="M49" s="127" t="s">
         <v>223</v>
       </c>
-      <c r="N49" s="138" t="s">
+      <c r="N49" s="127" t="s">
         <v>224</v>
       </c>
-      <c r="O49" s="138" t="s">
+      <c r="O49" s="127" t="s">
         <v>225</v>
       </c>
-      <c r="P49" s="138" t="s">
+      <c r="P49" s="127" t="s">
         <v>226</v>
       </c>
-      <c r="Q49" s="138" t="s">
+      <c r="Q49" s="127" t="s">
         <v>227</v>
       </c>
-      <c r="R49" s="138" t="s">
+      <c r="R49" s="127" t="s">
         <v>228</v>
       </c>
-      <c r="S49" s="138" t="s">
+      <c r="S49" s="127" t="s">
         <v>229</v>
       </c>
-      <c r="T49" s="138" t="s">
+      <c r="T49" s="127" t="s">
         <v>230</v>
       </c>
-      <c r="V49" s="205" t="s">
+      <c r="V49" s="191" t="s">
         <v>194</v>
       </c>
-      <c r="W49" s="205">
+      <c r="W49" s="191">
         <f t="shared" ref="W49:W62" si="0">COUNTIF($D$47:$D$60,V49)</f>
         <v>1</v>
       </c>
     </row>
     <row r="50" ht="55" spans="1:23">
-      <c r="A50" s="219">
+      <c r="A50" s="203">
         <v>4</v>
       </c>
-      <c r="B50" s="138" t="s">
+      <c r="B50" s="127" t="s">
         <v>173</v>
       </c>
-      <c r="C50" s="138" t="s">
+      <c r="C50" s="127" t="s">
         <v>231</v>
       </c>
-      <c r="D50" s="138" t="s">
+      <c r="D50" s="127" t="s">
         <v>232</v>
       </c>
-      <c r="E50" s="138" t="s">
+      <c r="E50" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="F50" s="138" t="s">
+      <c r="F50" s="127" t="s">
         <v>221</v>
       </c>
-      <c r="G50" s="190" t="s">
+      <c r="G50" s="176" t="s">
         <v>222</v>
       </c>
-      <c r="H50" s="138" t="str">
+      <c r="H50" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/AI-VIDEO-CREATIVE-WORKFLOWS/AI-VIDEO-CREATIVE-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I50" s="138" t="str">
+      <c r="I50" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bai-construction-timelapse-short-video%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J50" s="220">
+      <c r="J50" s="204">
         <v>46244</v>
       </c>
-      <c r="K50" s="220"/>
-      <c r="L50" s="138" t="s">
+      <c r="K50" s="204"/>
+      <c r="L50" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="M50" s="138" t="s">
+      <c r="M50" s="127" t="s">
         <v>223</v>
       </c>
-      <c r="N50" s="138" t="s">
+      <c r="N50" s="127" t="s">
         <v>233</v>
       </c>
-      <c r="O50" s="138" t="s">
+      <c r="O50" s="127" t="s">
         <v>234</v>
       </c>
-      <c r="P50" s="138" t="s">
+      <c r="P50" s="127" t="s">
         <v>235</v>
       </c>
-      <c r="Q50" s="138" t="s">
+      <c r="Q50" s="127" t="s">
         <v>227</v>
       </c>
-      <c r="R50" s="138" t="s">
+      <c r="R50" s="127" t="s">
         <v>236</v>
       </c>
-      <c r="S50" s="138" t="s">
+      <c r="S50" s="127" t="s">
         <v>237</v>
       </c>
-      <c r="T50" s="138" t="s">
+      <c r="T50" s="127" t="s">
         <v>238</v>
       </c>
-      <c r="V50" s="205" t="s">
+      <c r="V50" s="191" t="s">
         <v>239</v>
       </c>
-      <c r="W50" s="205">
+      <c r="W50" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" ht="28" spans="1:23">
-      <c r="A51" s="219">
+      <c r="A51" s="203">
         <v>5</v>
       </c>
-      <c r="B51" s="138" t="s">
+      <c r="B51" s="127" t="s">
         <v>240</v>
       </c>
-      <c r="C51" s="138" t="s">
+      <c r="C51" s="127" t="s">
         <v>241</v>
       </c>
-      <c r="D51" s="138" t="s">
+      <c r="D51" s="127" t="s">
         <v>242</v>
       </c>
-      <c r="E51" s="138" t="s">
+      <c r="E51" s="127" t="s">
         <v>141</v>
       </c>
-      <c r="F51" s="138" t="s">
+      <c r="F51" s="127" t="s">
         <v>195</v>
       </c>
-      <c r="G51" s="190" t="s">
+      <c r="G51" s="176" t="s">
         <v>196</v>
       </c>
-      <c r="H51" s="138" t="str">
+      <c r="H51" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/social-ai-clone-creative/social-ai-clone-creative-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I51" s="138" t="str">
+      <c r="I51" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bai_clone_creative%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J51" s="220">
+      <c r="J51" s="204">
         <v>46247</v>
       </c>
-      <c r="K51" s="220" t="s">
+      <c r="K51" s="204" t="s">
         <v>243</v>
       </c>
-      <c r="L51" s="138" t="str">
+      <c r="L51" s="127" t="str">
         <f>HYPERLINK("#'AI Clone Creative'!A1","Mở chi tiết")</f>
         <v>Mở chi tiết</v>
       </c>
-      <c r="M51" s="138" t="s">
+      <c r="M51" s="127" t="s">
         <v>244</v>
       </c>
-      <c r="N51" s="138" t="s">
+      <c r="N51" s="127" t="s">
         <v>245</v>
       </c>
-      <c r="O51" s="138" t="s">
+      <c r="O51" s="127" t="s">
         <v>246</v>
       </c>
-      <c r="P51" s="138" t="s">
+      <c r="P51" s="127" t="s">
         <v>247</v>
       </c>
-      <c r="Q51" s="138" t="s">
+      <c r="Q51" s="127" t="s">
         <v>248</v>
       </c>
-      <c r="R51" s="138" t="s">
+      <c r="R51" s="127" t="s">
         <v>249</v>
       </c>
-      <c r="S51" s="138" t="s">
+      <c r="S51" s="127" t="s">
         <v>250</v>
       </c>
-      <c r="T51" s="138" t="s">
+      <c r="T51" s="127" t="s">
         <v>251</v>
       </c>
-      <c r="V51" s="205" t="s">
+      <c r="V51" s="191" t="s">
         <v>220</v>
       </c>
-      <c r="W51" s="205">
+      <c r="W51" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:23">
-      <c r="A52" s="219">
+      <c r="A52" s="203">
         <v>6</v>
       </c>
-      <c r="B52" s="138" t="s">
+      <c r="B52" s="127" t="s">
         <v>252</v>
       </c>
-      <c r="C52" s="138" t="s">
+      <c r="C52" s="127" t="s">
         <v>253</v>
       </c>
-      <c r="D52" s="138" t="s">
+      <c r="D52" s="127" t="s">
         <v>254</v>
       </c>
-      <c r="E52" s="138" t="s">
+      <c r="E52" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="F52" s="138" t="s">
+      <c r="F52" s="127" t="s">
         <v>221</v>
       </c>
-      <c r="G52" s="190" t="s">
+      <c r="G52" s="176" t="s">
         <v>222</v>
       </c>
-      <c r="H52" s="138" t="str">
+      <c r="H52" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/social-single-static/social-single-static-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I52" s="138" t="str">
+      <c r="I52" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bhtml-carousel%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J52" s="220">
+      <c r="J52" s="204">
         <v>46238</v>
       </c>
-      <c r="K52" s="220"/>
-      <c r="L52" s="138" t="s">
+      <c r="K52" s="204"/>
+      <c r="L52" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="M52" s="138" t="s">
+      <c r="M52" s="127" t="s">
         <v>255</v>
       </c>
-      <c r="N52" s="138" t="s">
+      <c r="N52" s="127" t="s">
         <v>256</v>
       </c>
-      <c r="O52" s="138" t="s">
+      <c r="O52" s="127" t="s">
         <v>257</v>
       </c>
-      <c r="P52" s="138" t="s">
+      <c r="P52" s="127" t="s">
         <v>258</v>
       </c>
-      <c r="Q52" s="138" t="s">
+      <c r="Q52" s="127" t="s">
         <v>227</v>
       </c>
-      <c r="R52" s="138" t="s">
+      <c r="R52" s="127" t="s">
         <v>259</v>
       </c>
-      <c r="S52" s="138" t="s">
+      <c r="S52" s="127" t="s">
         <v>260</v>
       </c>
-      <c r="T52" s="138" t="s">
+      <c r="T52" s="127" t="s">
         <v>261</v>
       </c>
-      <c r="V52" s="205" t="s">
+      <c r="V52" s="191" t="s">
         <v>232</v>
       </c>
-      <c r="W52" s="205">
+      <c r="W52" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="53" ht="28" spans="1:23">
-      <c r="A53" s="219">
+      <c r="A53" s="203">
         <v>7</v>
       </c>
-      <c r="B53" s="138" t="s">
+      <c r="B53" s="127" t="s">
         <v>262</v>
       </c>
-      <c r="C53" s="138" t="s">
+      <c r="C53" s="127" t="s">
         <v>263</v>
       </c>
-      <c r="D53" s="138" t="s">
+      <c r="D53" s="127" t="s">
         <v>264</v>
       </c>
-      <c r="E53" s="138" t="s">
+      <c r="E53" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="F53" s="138" t="s">
+      <c r="F53" s="127" t="s">
         <v>221</v>
       </c>
-      <c r="G53" s="190" t="s">
+      <c r="G53" s="176" t="s">
         <v>222</v>
       </c>
-      <c r="H53" s="138" t="str">
+      <c r="H53" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/AI-VIDEO-CREATIVE-WORKFLOWS/AI-VIDEO-CREATIVE-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I53" s="138" t="str">
+      <c r="I53" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bhuman-short-video%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J53" s="220">
+      <c r="J53" s="204">
         <v>46222</v>
       </c>
-      <c r="K53" s="220"/>
-      <c r="L53" s="138" t="s">
+      <c r="K53" s="204"/>
+      <c r="L53" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="M53" s="138" t="s">
+      <c r="M53" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="N53" s="138" t="s">
+      <c r="N53" s="127" t="s">
         <v>265</v>
       </c>
-      <c r="O53" s="138" t="s">
+      <c r="O53" s="127" t="s">
         <v>266</v>
       </c>
-      <c r="P53" s="138" t="s">
+      <c r="P53" s="127" t="s">
         <v>267</v>
       </c>
-      <c r="Q53" s="138" t="s">
+      <c r="Q53" s="127" t="s">
         <v>268</v>
       </c>
-      <c r="R53" s="138" t="s">
+      <c r="R53" s="127" t="s">
         <v>269</v>
       </c>
-      <c r="S53" s="138" t="s">
+      <c r="S53" s="127" t="s">
         <v>270</v>
       </c>
-      <c r="T53" s="138" t="s">
+      <c r="T53" s="127" t="s">
         <v>271</v>
       </c>
-      <c r="V53" s="205" t="s">
+      <c r="V53" s="191" t="s">
         <v>272</v>
       </c>
-      <c r="W53" s="205">
+      <c r="W53" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" ht="41" spans="1:23">
-      <c r="A54" s="219">
+      <c r="A54" s="203">
         <v>8</v>
       </c>
-      <c r="B54" s="138" t="s">
+      <c r="B54" s="127" t="s">
         <v>273</v>
       </c>
-      <c r="C54" s="138" t="s">
+      <c r="C54" s="127" t="s">
         <v>274</v>
       </c>
-      <c r="D54" s="138" t="s">
+      <c r="D54" s="127" t="s">
         <v>275</v>
       </c>
-      <c r="E54" s="138" t="s">
+      <c r="E54" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="F54" s="138" t="s">
+      <c r="F54" s="127" t="s">
         <v>221</v>
       </c>
-      <c r="G54" s="190" t="s">
+      <c r="G54" s="176" t="s">
         <v>222</v>
       </c>
-      <c r="H54" s="138" t="str">
+      <c r="H54" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/social-single-static/social-single-static-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I54" s="138" t="str">
+      <c r="I54" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bimg-carousel%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J54" s="220">
+      <c r="J54" s="204">
         <v>46237</v>
       </c>
-      <c r="K54" s="220"/>
-      <c r="L54" s="138" t="s">
+      <c r="K54" s="204"/>
+      <c r="L54" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="M54" s="138" t="s">
+      <c r="M54" s="127" t="s">
         <v>255</v>
       </c>
-      <c r="N54" s="138" t="s">
+      <c r="N54" s="127" t="s">
         <v>276</v>
       </c>
-      <c r="O54" s="138" t="s">
+      <c r="O54" s="127" t="s">
         <v>277</v>
       </c>
-      <c r="P54" s="138" t="s">
+      <c r="P54" s="127" t="s">
         <v>278</v>
       </c>
-      <c r="Q54" s="138" t="s">
+      <c r="Q54" s="127" t="s">
         <v>279</v>
       </c>
-      <c r="R54" s="138" t="s">
+      <c r="R54" s="127" t="s">
         <v>280</v>
       </c>
-      <c r="S54" s="138" t="s">
+      <c r="S54" s="127" t="s">
         <v>281</v>
       </c>
-      <c r="T54" s="138" t="s">
+      <c r="T54" s="127" t="s">
         <v>282</v>
       </c>
-      <c r="V54" s="205" t="s">
+      <c r="V54" s="191" t="s">
         <v>254</v>
       </c>
-      <c r="W54" s="205">
+      <c r="W54" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="55" ht="28" spans="1:23">
-      <c r="A55" s="219">
+      <c r="A55" s="203">
         <v>9</v>
       </c>
-      <c r="B55" s="138" t="s">
+      <c r="B55" s="127" t="s">
         <v>283</v>
       </c>
-      <c r="C55" s="138" t="s">
+      <c r="C55" s="127" t="s">
         <v>284</v>
       </c>
-      <c r="D55" s="138" t="s">
+      <c r="D55" s="127" t="s">
         <v>285</v>
       </c>
-      <c r="E55" s="138" t="s">
+      <c r="E55" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="F55" s="138" t="s">
+      <c r="F55" s="127" t="s">
         <v>221</v>
       </c>
-      <c r="G55" s="190" t="s">
+      <c r="G55" s="176" t="s">
         <v>286</v>
       </c>
-      <c r="H55" s="138" t="str">
+      <c r="H55" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/social-single-static/social-single-static-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I55" s="138" t="str">
+      <c r="I55" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bindustry-news-html-summery%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J55" s="220">
+      <c r="J55" s="204">
         <v>46244</v>
       </c>
-      <c r="K55" s="220"/>
-      <c r="L55" s="138" t="s">
+      <c r="K55" s="204"/>
+      <c r="L55" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="M55" s="138" t="s">
+      <c r="M55" s="127" t="s">
         <v>287</v>
       </c>
-      <c r="N55" s="138" t="s">
+      <c r="N55" s="127" t="s">
         <v>288</v>
       </c>
-      <c r="O55" s="138" t="s">
+      <c r="O55" s="127" t="s">
         <v>289</v>
       </c>
-      <c r="P55" s="138" t="s">
+      <c r="P55" s="127" t="s">
         <v>290</v>
       </c>
-      <c r="Q55" s="138" t="s">
+      <c r="Q55" s="127" t="s">
         <v>291</v>
       </c>
-      <c r="R55" s="138" t="s">
+      <c r="R55" s="127" t="s">
         <v>292</v>
       </c>
-      <c r="S55" s="138" t="s">
+      <c r="S55" s="127" t="s">
         <v>293</v>
       </c>
-      <c r="T55" s="138" t="s">
+      <c r="T55" s="127" t="s">
         <v>294</v>
       </c>
-      <c r="V55" s="205" t="s">
+      <c r="V55" s="191" t="s">
         <v>264</v>
       </c>
-      <c r="W55" s="205">
+      <c r="W55" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="56" ht="28" spans="1:23">
-      <c r="A56" s="219">
+      <c r="A56" s="203">
         <v>10</v>
       </c>
-      <c r="B56" s="138" t="s">
+      <c r="B56" s="127" t="s">
         <v>295</v>
       </c>
-      <c r="C56" s="138" t="s">
+      <c r="C56" s="127" t="s">
         <v>296</v>
       </c>
-      <c r="D56" s="138" t="s">
+      <c r="D56" s="127" t="s">
         <v>297</v>
       </c>
-      <c r="E56" s="138" t="s">
+      <c r="E56" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="F56" s="138" t="s">
+      <c r="F56" s="127" t="s">
         <v>221</v>
       </c>
-      <c r="G56" s="190" t="s">
+      <c r="G56" s="176" t="s">
         <v>286</v>
       </c>
-      <c r="H56" s="138" t="str">
+      <c r="H56" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/AI-VIDEO-CREATIVE-WORKFLOWS/AI-VIDEO-CREATIVE-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I56" s="138" t="str">
+      <c r="I56" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bmotion-graphic%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J56" s="220">
+      <c r="J56" s="204">
         <v>46222</v>
       </c>
-      <c r="K56" s="220"/>
-      <c r="L56" s="138" t="s">
+      <c r="K56" s="204"/>
+      <c r="L56" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="M56" s="138" t="s">
+      <c r="M56" s="127" t="s">
         <v>298</v>
       </c>
-      <c r="N56" s="138" t="s">
+      <c r="N56" s="127" t="s">
         <v>299</v>
       </c>
-      <c r="O56" s="138" t="s">
+      <c r="O56" s="127" t="s">
         <v>300</v>
       </c>
-      <c r="P56" s="138" t="s">
+      <c r="P56" s="127" t="s">
         <v>301</v>
       </c>
-      <c r="Q56" s="138" t="s">
+      <c r="Q56" s="127" t="s">
         <v>302</v>
       </c>
-      <c r="R56" s="138" t="s">
+      <c r="R56" s="127" t="s">
         <v>303</v>
       </c>
-      <c r="S56" s="138" t="s">
+      <c r="S56" s="127" t="s">
         <v>270</v>
       </c>
-      <c r="T56" s="138" t="s">
+      <c r="T56" s="127" t="s">
         <v>304</v>
       </c>
-      <c r="V56" s="205" t="s">
+      <c r="V56" s="191" t="s">
         <v>275</v>
       </c>
-      <c r="W56" s="205">
+      <c r="W56" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="57" ht="41" spans="1:23">
-      <c r="A57" s="219">
+      <c r="A57" s="203">
         <v>11</v>
       </c>
-      <c r="B57" s="138" t="s">
+      <c r="B57" s="127" t="s">
         <v>305</v>
       </c>
-      <c r="C57" s="138" t="s">
+      <c r="C57" s="127" t="s">
         <v>306</v>
       </c>
-      <c r="D57" s="138" t="s">
+      <c r="D57" s="127" t="s">
         <v>307</v>
       </c>
-      <c r="E57" s="138" t="s">
+      <c r="E57" s="127" t="s">
         <v>133</v>
       </c>
-      <c r="F57" s="138" t="s">
+      <c r="F57" s="127" t="s">
         <v>195</v>
       </c>
-      <c r="G57" s="190" t="s">
+      <c r="G57" s="176" t="s">
         <v>196</v>
       </c>
-      <c r="H57" s="138" t="str">
+      <c r="H57" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/social-single-static/social-single-static-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I57" s="138" t="str">
+      <c r="I57" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bsingle-static%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J57" s="220">
+      <c r="J57" s="204">
         <v>46222</v>
       </c>
-      <c r="K57" s="220" t="s">
+      <c r="K57" s="204" t="s">
         <v>243</v>
       </c>
-      <c r="L57" s="138" t="str">
+      <c r="L57" s="127" t="str">
         <f>HYPERLINK("#'Single Static'!A1","Mở chi tiết")</f>
         <v>Mở chi tiết</v>
       </c>
-      <c r="M57" s="138" t="s">
+      <c r="M57" s="127" t="s">
         <v>255</v>
       </c>
-      <c r="N57" s="138" t="s">
+      <c r="N57" s="127" t="s">
         <v>276</v>
       </c>
-      <c r="O57" s="138" t="s">
+      <c r="O57" s="127" t="s">
         <v>308</v>
       </c>
-      <c r="P57" s="138" t="s">
+      <c r="P57" s="127" t="s">
         <v>309</v>
       </c>
-      <c r="Q57" s="138" t="s">
+      <c r="Q57" s="127" t="s">
         <v>310</v>
       </c>
-      <c r="R57" s="138" t="s">
+      <c r="R57" s="127" t="s">
         <v>311</v>
       </c>
-      <c r="S57" s="138" t="s">
+      <c r="S57" s="127" t="s">
         <v>312</v>
       </c>
-      <c r="T57" s="138" t="s">
+      <c r="T57" s="127" t="s">
         <v>313</v>
       </c>
-      <c r="V57" s="205" t="s">
+      <c r="V57" s="191" t="s">
         <v>285</v>
       </c>
-      <c r="W57" s="205">
+      <c r="W57" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="58" ht="28" spans="1:23">
-      <c r="A58" s="219">
+      <c r="A58" s="203">
         <v>12</v>
       </c>
-      <c r="B58" s="138" t="s">
+      <c r="B58" s="127" t="s">
         <v>314</v>
       </c>
-      <c r="C58" s="138" t="s">
+      <c r="C58" s="127" t="s">
         <v>315</v>
       </c>
-      <c r="D58" s="138" t="s">
+      <c r="D58" s="127" t="s">
         <v>316</v>
       </c>
-      <c r="E58" s="138" t="s">
+      <c r="E58" s="127" t="s">
         <v>149</v>
       </c>
-      <c r="F58" s="138" t="s">
+      <c r="F58" s="127" t="s">
         <v>221</v>
       </c>
-      <c r="G58" s="190" t="s">
+      <c r="G58" s="176" t="s">
         <v>286</v>
       </c>
-      <c r="H58" s="138" t="str">
+      <c r="H58" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/social-single-static/social-single-static-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I58" s="138" t="str">
+      <c r="I58" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/goal/%5Bsocial%5D_%5Bsplit-4-img%5D.md","Mở goal trên repo")</f>
         <v>Mở goal trên repo</v>
       </c>
-      <c r="J58" s="220">
+      <c r="J58" s="204">
         <v>46238</v>
       </c>
-      <c r="K58" s="220"/>
-      <c r="L58" s="138" t="s">
+      <c r="K58" s="204"/>
+      <c r="L58" s="127" t="s">
         <v>63</v>
       </c>
-      <c r="M58" s="138" t="s">
+      <c r="M58" s="127" t="s">
         <v>317</v>
       </c>
-      <c r="N58" s="138" t="s">
+      <c r="N58" s="127" t="s">
         <v>318</v>
       </c>
-      <c r="O58" s="138" t="s">
+      <c r="O58" s="127" t="s">
         <v>319</v>
       </c>
-      <c r="P58" s="138" t="s">
+      <c r="P58" s="127" t="s">
         <v>320</v>
       </c>
-      <c r="Q58" s="138" t="s">
+      <c r="Q58" s="127" t="s">
         <v>279</v>
       </c>
-      <c r="R58" s="138" t="s">
+      <c r="R58" s="127" t="s">
         <v>321</v>
       </c>
-      <c r="S58" s="138" t="s">
+      <c r="S58" s="127" t="s">
         <v>281</v>
       </c>
-      <c r="T58" s="138" t="s">
+      <c r="T58" s="127" t="s">
         <v>322</v>
       </c>
-      <c r="V58" s="205" t="s">
+      <c r="V58" s="191" t="s">
         <v>297</v>
       </c>
-      <c r="W58" s="205">
+      <c r="W58" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="59" ht="41" spans="1:23">
-      <c r="A59" s="219">
+      <c r="A59" s="203">
         <v>13</v>
       </c>
-      <c r="B59" s="138" t="s">
+      <c r="B59" s="127" t="s">
         <v>323</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="127" t="s">
         <v>324</v>
       </c>
-      <c r="D59" s="138" t="s">
+      <c r="D59" s="127" t="s">
         <v>325</v>
       </c>
-      <c r="E59" s="138" t="s">
+      <c r="E59" s="127" t="s">
         <v>158</v>
       </c>
-      <c r="F59" s="138" t="s">
+      <c r="F59" s="127" t="s">
         <v>195</v>
       </c>
-      <c r="G59" s="190" t="s">
+      <c r="G59" s="176" t="s">
         <v>196</v>
       </c>
-      <c r="H59" s="138" t="str">
+      <c r="H59" s="127" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/AI-VIDEO-CREATIVE-WORKFLOWS/AI-VIDEO-CREATIVE-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I59" s="138" t="s">
+      <c r="I59" s="127" t="s">
         <v>326</v>
       </c>
-      <c r="J59" s="220">
+      <c r="J59" s="204">
         <v>46252</v>
       </c>
-      <c r="K59" s="220"/>
-      <c r="L59" s="138" t="str">
+      <c r="K59" s="204"/>
+      <c r="L59" s="127" t="str">
         <f>HYPERLINK("#'Edit Source Mix'!A1","Mở chi tiết")</f>
         <v>Mở chi tiết</v>
       </c>
-      <c r="M59" s="138" t="s">
+      <c r="M59" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="N59" s="138" t="s">
+      <c r="N59" s="127" t="s">
         <v>327</v>
       </c>
-      <c r="O59" s="138" t="s">
+      <c r="O59" s="127" t="s">
         <v>328</v>
       </c>
-      <c r="P59" s="138" t="s">
+      <c r="P59" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="Q59" s="138" t="s">
+      <c r="Q59" s="127" t="s">
         <v>330</v>
       </c>
-      <c r="R59" s="138" t="s">
+      <c r="R59" s="127" t="s">
         <v>331</v>
       </c>
-      <c r="S59" s="138" t="s">
+      <c r="S59" s="127" t="s">
         <v>332</v>
       </c>
-      <c r="T59" s="138" t="s">
+      <c r="T59" s="127" t="s">
         <v>333</v>
       </c>
-      <c r="V59" s="205" t="s">
+      <c r="V59" s="191" t="s">
         <v>307</v>
       </c>
-      <c r="W59" s="205">
+      <c r="W59" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="60" ht="41" spans="1:23">
-      <c r="A60" s="221">
+      <c r="A60" s="205">
         <v>14</v>
       </c>
-      <c r="B60" s="147" t="s">
+      <c r="B60" s="131" t="s">
         <v>334</v>
       </c>
-      <c r="C60" s="147" t="s">
+      <c r="C60" s="131" t="s">
         <v>324</v>
       </c>
-      <c r="D60" s="147" t="s">
+      <c r="D60" s="131" t="s">
         <v>335</v>
       </c>
-      <c r="E60" s="147" t="s">
+      <c r="E60" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="F60" s="147" t="s">
+      <c r="F60" s="131" t="s">
         <v>16</v>
       </c>
-      <c r="G60" s="222" t="s">
+      <c r="G60" s="206" t="s">
         <v>222</v>
       </c>
-      <c r="H60" s="147" t="str">
+      <c r="H60" s="131" t="str">
         <f>HYPERLINK("file:///Users/test/Documents/AI Media/Hoài Nam/INFRA/DOCS/AI-VIDEO-CREATIVE-WORKFLOWS/AI-VIDEO-CREATIVE-WORKFLOW-DIAGRAM.png","Mở diagram")</f>
         <v>Mở diagram</v>
       </c>
-      <c r="I60" s="147" t="s">
+      <c r="I60" s="131" t="s">
         <v>326</v>
       </c>
-      <c r="J60" s="223">
+      <c r="J60" s="207">
         <v>46252</v>
       </c>
-      <c r="K60" s="223"/>
-      <c r="L60" s="147" t="str">
+      <c r="K60" s="207"/>
+      <c r="L60" s="131" t="str">
         <f>HYPERLINK("#'HTML Video Dropped'!A1","Mở chi tiết")</f>
         <v>Mở chi tiết</v>
       </c>
-      <c r="M60" s="147" t="s">
+      <c r="M60" s="131" t="s">
         <v>48</v>
       </c>
-      <c r="N60" s="147" t="s">
+      <c r="N60" s="131" t="s">
         <v>336</v>
       </c>
-      <c r="O60" s="147" t="s">
+      <c r="O60" s="131" t="s">
         <v>337</v>
       </c>
-      <c r="P60" s="147" t="s">
+      <c r="P60" s="131" t="s">
         <v>338</v>
       </c>
-      <c r="Q60" s="147" t="s">
+      <c r="Q60" s="131" t="s">
         <v>339</v>
       </c>
-      <c r="R60" s="147" t="s">
+      <c r="R60" s="131" t="s">
         <v>340</v>
       </c>
-      <c r="S60" s="147" t="s">
+      <c r="S60" s="131" t="s">
         <v>341</v>
       </c>
-      <c r="T60" s="147" t="s">
+      <c r="T60" s="131" t="s">
         <v>342</v>
       </c>
-      <c r="V60" s="205" t="s">
+      <c r="V60" s="191" t="s">
         <v>316</v>
       </c>
-      <c r="W60" s="205">
+      <c r="W60" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:23">
-      <c r="V61" s="205" t="s">
+      <c r="V61" s="191" t="s">
         <v>325</v>
       </c>
-      <c r="W61" s="205">
+      <c r="W61" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="62" ht="17.6" spans="1:23">
-      <c r="A62" s="224" t="s">
+      <c r="A62" s="208" t="s">
         <v>343</v>
       </c>
-      <c r="B62" s="224"/>
-      <c r="C62" s="224"/>
-      <c r="D62" s="224"/>
-      <c r="E62" s="224"/>
-      <c r="F62" s="224"/>
-      <c r="G62" s="224"/>
-      <c r="H62" s="224"/>
-      <c r="I62" s="224"/>
-      <c r="J62" s="224"/>
-      <c r="K62" s="224"/>
-      <c r="L62" s="224"/>
-      <c r="M62" s="224"/>
-      <c r="N62" s="224"/>
-      <c r="O62" s="224"/>
-      <c r="P62" s="224"/>
-      <c r="Q62" s="224"/>
-      <c r="R62" s="224"/>
-      <c r="S62" s="224"/>
-      <c r="T62" s="224"/>
-      <c r="V62" s="205" t="s">
+      <c r="B62" s="208"/>
+      <c r="C62" s="208"/>
+      <c r="D62" s="208"/>
+      <c r="E62" s="208"/>
+      <c r="F62" s="208"/>
+      <c r="G62" s="208"/>
+      <c r="H62" s="208"/>
+      <c r="I62" s="208"/>
+      <c r="J62" s="208"/>
+      <c r="K62" s="208"/>
+      <c r="L62" s="208"/>
+      <c r="M62" s="208"/>
+      <c r="N62" s="208"/>
+      <c r="O62" s="208"/>
+      <c r="P62" s="208"/>
+      <c r="Q62" s="208"/>
+      <c r="R62" s="208"/>
+      <c r="S62" s="208"/>
+      <c r="T62" s="208"/>
+      <c r="V62" s="191" t="s">
         <v>335</v>
       </c>
-      <c r="W62" s="205">
+      <c r="W62" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:23">
-      <c r="A63" s="182"/>
-      <c r="B63" s="182"/>
-      <c r="C63" s="182"/>
-      <c r="D63" s="182"/>
-      <c r="E63" s="182"/>
-      <c r="F63" s="182"/>
-      <c r="G63" s="182"/>
-      <c r="H63" s="182"/>
+      <c r="A63" s="168"/>
+      <c r="B63" s="168"/>
+      <c r="C63" s="168"/>
+      <c r="D63" s="168"/>
+      <c r="E63" s="168"/>
+      <c r="F63" s="168"/>
+      <c r="G63" s="168"/>
+      <c r="H63" s="168"/>
     </row>
     <row r="64" spans="1:23">
-      <c r="A64" s="225" t="s">
+      <c r="A64" s="209" t="s">
         <v>70</v>
       </c>
-      <c r="B64" s="225" t="s">
+      <c r="B64" s="209" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="225" t="s">
+      <c r="C64" s="209" t="s">
         <v>73</v>
       </c>
-      <c r="D64" s="225" t="s">
+      <c r="D64" s="209" t="s">
         <v>345</v>
       </c>
-      <c r="E64" s="225" t="s">
+      <c r="E64" s="209" t="s">
         <v>346</v>
       </c>
-      <c r="F64" s="225" t="s">
+      <c r="F64" s="209" t="s">
         <v>347</v>
       </c>
-      <c r="G64" s="225" t="s">
+      <c r="G64" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="H64" s="225" t="s">
+      <c r="H64" s="209" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="65" ht="28" spans="1:8">
-      <c r="A65" s="226">
+      <c r="A65" s="210">
         <v>1</v>
       </c>
-      <c r="B65" s="133" t="s">
+      <c r="B65" s="122" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="133" t="s">
+      <c r="C65" s="122" t="s">
         <v>349</v>
       </c>
-      <c r="D65" s="133" t="str">
+      <c r="D65" s="122" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/notion2goal/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E65" s="133" t="s">
+      <c r="E65" s="122" t="s">
         <v>350</v>
       </c>
-      <c r="F65" s="133" t="s">
+      <c r="F65" s="122" t="s">
         <v>351</v>
       </c>
-      <c r="G65" s="133" t="s">
+      <c r="G65" s="122" t="s">
         <v>352</v>
       </c>
-      <c r="H65" s="136" t="s">
+      <c r="H65" s="125" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="219">
+      <c r="A66" s="203">
         <v>2</v>
       </c>
-      <c r="B66" s="138" t="s">
+      <c r="B66" s="127" t="s">
         <v>354</v>
       </c>
-      <c r="C66" s="138" t="s">
+      <c r="C66" s="127" t="s">
         <v>355</v>
       </c>
-      <c r="D66" s="138" t="str">
+      <c r="D66" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/wiki-query/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E66" s="138" t="s">
+      <c r="E66" s="127" t="s">
         <v>356</v>
       </c>
-      <c r="F66" s="138" t="s">
+      <c r="F66" s="127" t="s">
         <v>357</v>
       </c>
-      <c r="G66" s="138" t="s">
+      <c r="G66" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H66" s="141" t="s">
+      <c r="H66" s="130" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="67" ht="28" spans="1:8">
-      <c r="A67" s="219">
+      <c r="A67" s="203">
         <v>3</v>
       </c>
-      <c r="B67" s="138" t="s">
+      <c r="B67" s="127" t="s">
         <v>124</v>
       </c>
-      <c r="C67" s="138" t="s">
+      <c r="C67" s="127" t="s">
         <v>358</v>
       </c>
-      <c r="D67" s="138" t="str">
+      <c r="D67" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/gemini-tts-timing/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E67" s="138" t="s">
+      <c r="E67" s="127" t="s">
         <v>359</v>
       </c>
-      <c r="F67" s="138" t="s">
+      <c r="F67" s="127" t="s">
         <v>360</v>
       </c>
-      <c r="G67" s="138" t="s">
+      <c r="G67" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H67" s="141" t="s">
+      <c r="H67" s="130" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="68" ht="41" spans="1:8">
-      <c r="A68" s="219">
+      <c r="A68" s="203">
         <v>4</v>
       </c>
-      <c r="B68" s="138" t="s">
+      <c r="B68" s="127" t="s">
         <v>361</v>
       </c>
-      <c r="C68" s="138" t="s">
+      <c r="C68" s="127" t="s">
         <v>362</v>
       </c>
-      <c r="D68" s="138" t="str">
+      <c r="D68" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/write-shooting-script/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E68" s="138" t="s">
+      <c r="E68" s="127" t="s">
         <v>363</v>
       </c>
-      <c r="F68" s="138" t="s">
+      <c r="F68" s="127" t="s">
         <v>364</v>
       </c>
-      <c r="G68" s="138" t="s">
+      <c r="G68" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H68" s="141" t="s">
+      <c r="H68" s="130" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="69" ht="28" spans="1:8">
-      <c r="A69" s="219">
+      <c r="A69" s="203">
         <v>5</v>
       </c>
-      <c r="B69" s="138" t="s">
+      <c r="B69" s="127" t="s">
         <v>366</v>
       </c>
-      <c r="C69" s="138" t="s">
+      <c r="C69" s="127" t="s">
         <v>367</v>
       </c>
-      <c r="D69" s="138" t="str">
+      <c r="D69" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/write-ai-ugc-video-sequence-script/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E69" s="138" t="s">
+      <c r="E69" s="127" t="s">
         <v>368</v>
       </c>
-      <c r="F69" s="138" t="s">
+      <c r="F69" s="127" t="s">
         <v>369</v>
       </c>
-      <c r="G69" s="138" t="s">
+      <c r="G69" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H69" s="141" t="s">
+      <c r="H69" s="130" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="70" ht="28" spans="1:8">
-      <c r="A70" s="219">
+      <c r="A70" s="203">
         <v>6</v>
       </c>
-      <c r="B70" s="138" t="s">
+      <c r="B70" s="127" t="s">
         <v>370</v>
       </c>
-      <c r="C70" s="138" t="s">
+      <c r="C70" s="127" t="s">
         <v>371</v>
       </c>
-      <c r="D70" s="138" t="str">
+      <c r="D70" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/tea-ugc-ai-realism/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E70" s="138" t="s">
+      <c r="E70" s="127" t="s">
         <v>372</v>
       </c>
-      <c r="F70" s="138" t="s">
+      <c r="F70" s="127" t="s">
         <v>373</v>
       </c>
-      <c r="G70" s="138" t="s">
+      <c r="G70" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H70" s="141" t="s">
+      <c r="H70" s="130" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="71" ht="55" spans="1:8">
-      <c r="A71" s="219">
+      <c r="A71" s="203">
         <v>7</v>
       </c>
-      <c r="B71" s="138" t="s">
+      <c r="B71" s="127" t="s">
         <v>374</v>
       </c>
-      <c r="C71" s="138" t="s">
+      <c r="C71" s="127" t="s">
         <v>375</v>
       </c>
-      <c r="D71" s="138" t="str">
+      <c r="D71" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/photography-direction/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E71" s="138" t="s">
+      <c r="E71" s="127" t="s">
         <v>376</v>
       </c>
-      <c r="F71" s="138" t="s">
+      <c r="F71" s="127" t="s">
         <v>377</v>
       </c>
-      <c r="G71" s="138" t="s">
+      <c r="G71" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H71" s="141" t="s">
+      <c r="H71" s="130" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="72" ht="55" spans="1:8">
-      <c r="A72" s="219">
+      <c r="A72" s="203">
         <v>8</v>
       </c>
-      <c r="B72" s="138" t="s">
+      <c r="B72" s="127" t="s">
         <v>379</v>
       </c>
-      <c r="C72" s="138" t="s">
+      <c r="C72" s="127" t="s">
         <v>380</v>
       </c>
-      <c r="D72" s="138" t="str">
+      <c r="D72" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/creative-direction/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E72" s="138" t="s">
+      <c r="E72" s="127" t="s">
         <v>381</v>
       </c>
-      <c r="F72" s="138" t="s">
+      <c r="F72" s="127" t="s">
         <v>377</v>
       </c>
-      <c r="G72" s="138" t="s">
+      <c r="G72" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H72" s="141" t="s">
+      <c r="H72" s="130" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="73" ht="28" spans="1:8">
-      <c r="A73" s="219">
+      <c r="A73" s="203">
         <v>9</v>
       </c>
-      <c r="B73" s="138" t="s">
+      <c r="B73" s="127" t="s">
         <v>383</v>
       </c>
-      <c r="C73" s="138" t="s">
+      <c r="C73" s="127" t="s">
         <v>384</v>
       </c>
-      <c r="D73" s="138" t="str">
+      <c r="D73" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/element-resolver/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E73" s="138" t="s">
+      <c r="E73" s="127" t="s">
         <v>385</v>
       </c>
-      <c r="F73" s="138" t="s">
+      <c r="F73" s="127" t="s">
         <v>386</v>
       </c>
-      <c r="G73" s="138" t="s">
+      <c r="G73" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H73" s="141" t="s">
+      <c r="H73" s="130" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="74" ht="55" spans="1:8">
-      <c r="A74" s="219">
+      <c r="A74" s="203">
         <v>10</v>
       </c>
-      <c r="B74" s="138" t="s">
+      <c r="B74" s="127" t="s">
         <v>388</v>
       </c>
-      <c r="C74" s="138" t="s">
+      <c r="C74" s="127" t="s">
         <v>389</v>
       </c>
-      <c r="D74" s="138" t="str">
+      <c r="D74" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/acad-image-gen/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E74" s="138" t="s">
+      <c r="E74" s="127" t="s">
         <v>390</v>
       </c>
-      <c r="F74" s="138" t="s">
+      <c r="F74" s="127" t="s">
         <v>391</v>
       </c>
-      <c r="G74" s="138" t="s">
+      <c r="G74" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H74" s="141" t="s">
+      <c r="H74" s="130" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="75" ht="28" spans="1:8">
-      <c r="A75" s="219">
+      <c r="A75" s="203">
         <v>11</v>
       </c>
-      <c r="B75" s="138" t="s">
+      <c r="B75" s="127" t="s">
         <v>392</v>
       </c>
-      <c r="C75" s="138" t="s">
+      <c r="C75" s="127" t="s">
         <v>393</v>
       </c>
-      <c r="D75" s="138" t="str">
+      <c r="D75" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/video-thumbnail/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E75" s="138" t="s">
+      <c r="E75" s="127" t="s">
         <v>394</v>
       </c>
-      <c r="F75" s="138" t="s">
+      <c r="F75" s="127" t="s">
         <v>395</v>
       </c>
-      <c r="G75" s="138" t="s">
+      <c r="G75" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H75" s="141" t="s">
+      <c r="H75" s="130" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="76" ht="28" spans="1:8">
-      <c r="A76" s="219">
+      <c r="A76" s="203">
         <v>12</v>
       </c>
-      <c r="B76" s="138" t="s">
+      <c r="B76" s="127" t="s">
         <v>396</v>
       </c>
-      <c r="C76" s="138" t="s">
+      <c r="C76" s="127" t="s">
         <v>397</v>
       </c>
-      <c r="D76" s="138" t="str">
+      <c r="D76" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/video_modules/flowkit/","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E76" s="138" t="s">
+      <c r="E76" s="127" t="s">
         <v>398</v>
       </c>
-      <c r="F76" s="138" t="s">
+      <c r="F76" s="127" t="s">
         <v>399</v>
       </c>
-      <c r="G76" s="138" t="s">
+      <c r="G76" s="127" t="s">
         <v>400</v>
       </c>
-      <c r="H76" s="141" t="s">
+      <c r="H76" s="130" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="77" ht="28" spans="1:8">
-      <c r="A77" s="219">
+      <c r="A77" s="203">
         <v>13</v>
       </c>
-      <c r="B77" s="138" t="s">
+      <c r="B77" s="127" t="s">
         <v>401</v>
       </c>
-      <c r="C77" s="138" t="s">
+      <c r="C77" s="127" t="s">
         <v>402</v>
       </c>
-      <c r="D77" s="138" t="str">
+      <c r="D77" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/video_modules/flowkit/","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E77" s="138" t="s">
+      <c r="E77" s="127" t="s">
         <v>403</v>
       </c>
-      <c r="F77" s="138" t="s">
+      <c r="F77" s="127" t="s">
         <v>399</v>
       </c>
-      <c r="G77" s="138" t="s">
+      <c r="G77" s="127" t="s">
         <v>400</v>
       </c>
-      <c r="H77" s="141" t="s">
+      <c r="H77" s="130" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="78" ht="55" spans="1:8">
-      <c r="A78" s="219">
+      <c r="A78" s="203">
         <v>14</v>
       </c>
-      <c r="B78" s="138" t="s">
+      <c r="B78" s="127" t="s">
         <v>404</v>
       </c>
-      <c r="C78" s="138" t="s">
+      <c r="C78" s="127" t="s">
         <v>405</v>
       </c>
-      <c r="D78" s="138" t="str">
+      <c r="D78" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/flowkit-nano-banana-image-gen/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E78" s="138" t="s">
+      <c r="E78" s="127" t="s">
         <v>406</v>
       </c>
-      <c r="F78" s="138" t="s">
+      <c r="F78" s="127" t="s">
         <v>407</v>
       </c>
-      <c r="G78" s="138" t="s">
+      <c r="G78" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H78" s="141" t="s">
+      <c r="H78" s="130" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="79" ht="28" spans="1:8">
-      <c r="A79" s="219">
+      <c r="A79" s="203">
         <v>15</v>
       </c>
-      <c r="B79" s="138" t="s">
+      <c r="B79" s="127" t="s">
         <v>408</v>
       </c>
-      <c r="C79" s="138" t="s">
+      <c r="C79" s="127" t="s">
         <v>409</v>
       </c>
-      <c r="D79" s="138" t="str">
+      <c r="D79" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/video_modules/flowkit/","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E79" s="138" t="s">
+      <c r="E79" s="127" t="s">
         <v>410</v>
       </c>
-      <c r="F79" s="138" t="s">
+      <c r="F79" s="127" t="s">
         <v>411</v>
       </c>
-      <c r="G79" s="138" t="s">
+      <c r="G79" s="127" t="s">
         <v>400</v>
       </c>
-      <c r="H79" s="141" t="s">
+      <c r="H79" s="130" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="80" ht="28" spans="1:8">
-      <c r="A80" s="219">
+      <c r="A80" s="203">
         <v>16</v>
       </c>
-      <c r="B80" s="138" t="s">
+      <c r="B80" s="127" t="s">
         <v>412</v>
       </c>
-      <c r="C80" s="138" t="s">
+      <c r="C80" s="127" t="s">
         <v>413</v>
       </c>
-      <c r="D80" s="138" t="str">
+      <c r="D80" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/video_modules/flowkit/","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E80" s="138" t="s">
+      <c r="E80" s="127" t="s">
         <v>414</v>
       </c>
-      <c r="F80" s="138" t="s">
+      <c r="F80" s="127" t="s">
         <v>415</v>
       </c>
-      <c r="G80" s="138" t="s">
+      <c r="G80" s="127" t="s">
         <v>400</v>
       </c>
-      <c r="H80" s="141" t="s">
+      <c r="H80" s="130" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="81" ht="28" spans="1:8">
-      <c r="A81" s="219">
+      <c r="A81" s="203">
         <v>17</v>
       </c>
-      <c r="B81" s="138" t="s">
+      <c r="B81" s="127" t="s">
         <v>416</v>
       </c>
-      <c r="C81" s="138" t="s">
+      <c r="C81" s="127" t="s">
         <v>417</v>
       </c>
-      <c r="D81" s="138" t="str">
+      <c r="D81" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/ffmpeg-upscale-video/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E81" s="138" t="s">
+      <c r="E81" s="127" t="s">
         <v>418</v>
       </c>
-      <c r="F81" s="138" t="s">
+      <c r="F81" s="127" t="s">
         <v>415</v>
       </c>
-      <c r="G81" s="138" t="s">
+      <c r="G81" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H81" s="141" t="s">
+      <c r="H81" s="130" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="82" ht="41" spans="1:8">
-      <c r="A82" s="219">
+      <c r="A82" s="203">
         <v>18</v>
       </c>
-      <c r="B82" s="138" t="s">
+      <c r="B82" s="127" t="s">
         <v>420</v>
       </c>
-      <c r="C82" s="138" t="s">
+      <c r="C82" s="127" t="s">
         <v>421</v>
       </c>
-      <c r="D82" s="138" t="str">
+      <c r="D82" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/%5Bhtml-video%5D-post-production-qa-broll-overlay/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E82" s="138" t="s">
+      <c r="E82" s="127" t="s">
         <v>422</v>
       </c>
-      <c r="F82" s="138" t="s">
+      <c r="F82" s="127" t="s">
         <v>423</v>
       </c>
-      <c r="G82" s="138" t="s">
+      <c r="G82" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H82" s="141" t="s">
+      <c r="H82" s="130" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="83" ht="28" spans="1:8">
-      <c r="A83" s="219">
+      <c r="A83" s="203">
         <v>19</v>
       </c>
-      <c r="B83" s="138" t="s">
+      <c r="B83" s="127" t="s">
         <v>425</v>
       </c>
-      <c r="C83" s="138" t="s">
+      <c r="C83" s="127" t="s">
         <v>426</v>
       </c>
-      <c r="D83" s="138" t="str">
+      <c r="D83" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/%5Bhtml-video%5D-subtitle-burn-talking-head/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E83" s="138" t="s">
+      <c r="E83" s="127" t="s">
         <v>427</v>
       </c>
-      <c r="F83" s="138" t="s">
+      <c r="F83" s="127" t="s">
         <v>415</v>
       </c>
-      <c r="G83" s="138" t="s">
+      <c r="G83" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H83" s="141" t="s">
+      <c r="H83" s="130" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="84" ht="28" spans="1:8">
-      <c r="A84" s="219">
+      <c r="A84" s="203">
         <v>20</v>
       </c>
-      <c r="B84" s="138" t="s">
+      <c r="B84" s="127" t="s">
         <v>428</v>
       </c>
-      <c r="C84" s="138" t="s">
+      <c r="C84" s="127" t="s">
         <v>429</v>
       </c>
-      <c r="D84" s="138" t="str">
+      <c r="D84" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/%5Bhtml-video%5D-audio-mix/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E84" s="138" t="s">
+      <c r="E84" s="127" t="s">
         <v>430</v>
       </c>
-      <c r="F84" s="138" t="s">
+      <c r="F84" s="127" t="s">
         <v>415</v>
       </c>
-      <c r="G84" s="138" t="s">
+      <c r="G84" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H84" s="141" t="s">
+      <c r="H84" s="130" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="219">
+      <c r="A85" s="203">
         <v>21</v>
       </c>
-      <c r="B85" s="138" t="s">
+      <c r="B85" s="127" t="s">
         <v>431</v>
       </c>
-      <c r="C85" s="138" t="s">
+      <c r="C85" s="127" t="s">
         <v>432</v>
       </c>
-      <c r="D85" s="138" t="str">
+      <c r="D85" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/notion-upload/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E85" s="138" t="s">
+      <c r="E85" s="127" t="s">
         <v>433</v>
       </c>
-      <c r="F85" s="138" t="s">
+      <c r="F85" s="127" t="s">
         <v>195</v>
       </c>
-      <c r="G85" s="138" t="s">
+      <c r="G85" s="127" t="s">
         <v>434</v>
       </c>
-      <c r="H85" s="141" t="s">
+      <c r="H85" s="130" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="86" ht="41" spans="1:8">
-      <c r="A86" s="219">
+      <c r="A86" s="203">
         <v>22</v>
       </c>
-      <c r="B86" s="138" t="s">
+      <c r="B86" s="127" t="s">
         <v>435</v>
       </c>
-      <c r="C86" s="138" t="s">
+      <c r="C86" s="127" t="s">
         <v>436</v>
       </c>
-      <c r="D86" s="138" t="str">
+      <c r="D86" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/gpt-img-2-gen/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E86" s="138" t="s">
+      <c r="E86" s="127" t="s">
         <v>437</v>
       </c>
-      <c r="F86" s="138" t="s">
+      <c r="F86" s="127" t="s">
         <v>391</v>
       </c>
-      <c r="G86" s="138" t="s">
+      <c r="G86" s="127" t="s">
         <v>438</v>
       </c>
-      <c r="H86" s="141" t="s">
+      <c r="H86" s="130" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="219">
+      <c r="A87" s="203">
         <v>23</v>
       </c>
-      <c r="B87" s="138" t="s">
+      <c r="B87" s="127" t="s">
         <v>440</v>
       </c>
-      <c r="C87" s="138" t="s">
+      <c r="C87" s="127" t="s">
         <v>441</v>
       </c>
-      <c r="D87" s="138" t="str">
+      <c r="D87" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/split-4-image/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E87" s="138" t="s">
+      <c r="E87" s="127" t="s">
         <v>442</v>
       </c>
-      <c r="F87" s="138" t="s">
+      <c r="F87" s="127" t="s">
         <v>443</v>
       </c>
-      <c r="G87" s="138" t="s">
+      <c r="G87" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H87" s="141" t="s">
+      <c r="H87" s="130" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="219">
+      <c r="A88" s="203">
         <v>24</v>
       </c>
-      <c r="B88" s="138" t="s">
+      <c r="B88" s="127" t="s">
         <v>166</v>
       </c>
-      <c r="C88" s="138" t="s">
+      <c r="C88" s="127" t="s">
         <v>444</v>
       </c>
-      <c r="D88" s="138" t="str">
+      <c r="D88" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/html-carousel-gen/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E88" s="138" t="s">
+      <c r="E88" s="127" t="s">
         <v>445</v>
       </c>
-      <c r="F88" s="138" t="s">
+      <c r="F88" s="127" t="s">
         <v>446</v>
       </c>
-      <c r="G88" s="138" t="s">
+      <c r="G88" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H88" s="141" t="s">
+      <c r="H88" s="130" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="89" ht="28" spans="1:8">
-      <c r="A89" s="219">
+      <c r="A89" s="203">
         <v>25</v>
       </c>
-      <c r="B89" s="138" t="s">
+      <c r="B89" s="127" t="s">
         <v>447</v>
       </c>
-      <c r="C89" s="138" t="s">
+      <c r="C89" s="127" t="s">
         <v>448</v>
       </c>
-      <c r="D89" s="138" t="str">
+      <c r="D89" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/html-creative-direction/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E89" s="138" t="s">
+      <c r="E89" s="127" t="s">
         <v>449</v>
       </c>
-      <c r="F89" s="138" t="s">
+      <c r="F89" s="127" t="s">
         <v>450</v>
       </c>
-      <c r="G89" s="138" t="s">
+      <c r="G89" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H89" s="141" t="s">
+      <c r="H89" s="130" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="219">
+      <c r="A90" s="203">
         <v>26</v>
       </c>
-      <c r="B90" s="138" t="s">
+      <c r="B90" s="127" t="s">
         <v>174</v>
       </c>
-      <c r="C90" s="138" t="s">
+      <c r="C90" s="127" t="s">
         <v>451</v>
       </c>
-      <c r="D90" s="138" t="str">
+      <c r="D90" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/gemini-veo-3.1-video-gen/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E90" s="138" t="s">
+      <c r="E90" s="127" t="s">
         <v>452</v>
       </c>
-      <c r="F90" s="138" t="s">
+      <c r="F90" s="127" t="s">
         <v>453</v>
       </c>
-      <c r="G90" s="138" t="s">
+      <c r="G90" s="127" t="s">
         <v>438</v>
       </c>
-      <c r="H90" s="141" t="s">
+      <c r="H90" s="130" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="219">
+      <c r="A91" s="203">
         <v>27</v>
       </c>
-      <c r="B91" s="138" t="s">
+      <c r="B91" s="127" t="s">
         <v>454</v>
       </c>
-      <c r="C91" s="138" t="s">
+      <c r="C91" s="127" t="s">
         <v>455</v>
       </c>
-      <c r="D91" s="138" t="str">
+      <c r="D91" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/ai-timelapse-video/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E91" s="138" t="s">
+      <c r="E91" s="127" t="s">
         <v>456</v>
       </c>
-      <c r="F91" s="138" t="s">
+      <c r="F91" s="127" t="s">
         <v>457</v>
       </c>
-      <c r="G91" s="138" t="s">
+      <c r="G91" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H91" s="141" t="s">
+      <c r="H91" s="130" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="219">
+      <c r="A92" s="203">
         <v>28</v>
       </c>
-      <c r="B92" s="138" t="s">
+      <c r="B92" s="127" t="s">
         <v>458</v>
       </c>
-      <c r="C92" s="138" t="s">
+      <c r="C92" s="127" t="s">
         <v>459</v>
       </c>
-      <c r="D92" s="138" t="str">
+      <c r="D92" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/construction-sequence-brainstorm/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E92" s="138" t="s">
+      <c r="E92" s="127" t="s">
         <v>460</v>
       </c>
-      <c r="F92" s="138" t="s">
+      <c r="F92" s="127" t="s">
         <v>461</v>
       </c>
-      <c r="G92" s="138" t="s">
+      <c r="G92" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H92" s="141" t="s">
+      <c r="H92" s="130" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="219">
+      <c r="A93" s="203">
         <v>29</v>
       </c>
-      <c r="B93" s="138" t="s">
+      <c r="B93" s="127" t="s">
         <v>462</v>
       </c>
-      <c r="C93" s="138" t="s">
+      <c r="C93" s="127" t="s">
         <v>463</v>
       </c>
-      <c r="D93" s="138" t="str">
+      <c r="D93" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/write-ai-commercial-video-sequence-script/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E93" s="138" t="s">
+      <c r="E93" s="127" t="s">
         <v>464</v>
       </c>
-      <c r="F93" s="138" t="s">
+      <c r="F93" s="127" t="s">
         <v>465</v>
       </c>
-      <c r="G93" s="138" t="s">
+      <c r="G93" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H93" s="141" t="s">
+      <c r="H93" s="130" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="219">
+      <c r="A94" s="203">
         <v>30</v>
       </c>
-      <c r="B94" s="138" t="s">
+      <c r="B94" s="127" t="s">
         <v>466</v>
       </c>
-      <c r="C94" s="138" t="s">
+      <c r="C94" s="127" t="s">
         <v>467</v>
       </c>
-      <c r="D94" s="138" t="str">
+      <c r="D94" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/.agents/skills/write-ai-timelapse-video-sequence-script/SKILL.md","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E94" s="138" t="s">
+      <c r="E94" s="127" t="s">
         <v>468</v>
       </c>
-      <c r="F94" s="138" t="s">
+      <c r="F94" s="127" t="s">
         <v>457</v>
       </c>
-      <c r="G94" s="138" t="s">
+      <c r="G94" s="127" t="s">
         <v>352</v>
       </c>
-      <c r="H94" s="141" t="s">
+      <c r="H94" s="130" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="95" ht="28" spans="1:8">
-      <c r="A95" s="219">
+      <c r="A95" s="203">
         <v>31</v>
       </c>
-      <c r="B95" s="138" t="s">
+      <c r="B95" s="127" t="s">
         <v>469</v>
       </c>
-      <c r="C95" s="138" t="s">
+      <c r="C95" s="127" t="s">
         <v>470</v>
       </c>
-      <c r="D95" s="138" t="str">
+      <c r="D95" s="127" t="str">
         <f>HYPERLINK("https://github.com/brucemakeurname/AI-media-Agent/blob/main/PRODUCTION/video_modules/talking-head-editing/","Mở skill/source")</f>
         <v>Mở skill/source</v>
       </c>
-      <c r="E95" s="138" t="s">
+      <c r="E95" s="127" t="s">
         <v>471</v>
       </c>
-      <c r="F95" s="138" t="s">
+      <c r="F95" s="127" t="s">
         <v>472</v>
       </c>
-      <c r="G95" s="138" t="s">
+      <c r="G95" s="127" t="s">
         <v>473</v>
       </c>
-      <c r="H95" s="141" t="s">
+      <c r="H95" s="130" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="96" ht="28" spans="1:8">
-      <c r="A96" s="219">
+      <c r="A96" s="203">
         <v>32</v>
       </c>
-      <c r="B96" s="138" t="s">
+      <c r="B96" s="127" t="s">
         <v>474</v>
       </c>
-      <c r="C96" s="138" t="s">
+      <c r="C96" s="127" t="s">
         <v>475</v>
       </c>
-      <c r="D96" s="138" t="s">
+      <c r="D96" s="127" t="s">
         <v>476</v>
       </c>
-      <c r="E96" s="138" t="s">
+      <c r="E96" s="127" t="s">
         <v>477</v>
       </c>
-      <c r="F96" s="138" t="s">
+      <c r="F96" s="127" t="s">
         <v>478</v>
       </c>
-      <c r="G96" s="138" t="s">
+      <c r="G96" s="127" t="s">
         <v>479</v>
       </c>
-      <c r="H96" s="141" t="s">
+      <c r="H96" s="130" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="97" ht="28" spans="1:20">
-      <c r="A97" s="221">
+      <c r="A97" s="205">
         <v>33</v>
       </c>
-      <c r="B97" s="147" t="s">
+      <c r="B97" s="131" t="s">
         <v>480</v>
       </c>
-      <c r="C97" s="147" t="s">
+      <c r="C97" s="131" t="s">
         <v>481</v>
       </c>
-      <c r="D97" s="147" t="s">
+      <c r="D97" s="131" t="s">
         <v>482</v>
       </c>
-      <c r="E97" s="147" t="s">
+      <c r="E97" s="131" t="s">
         <v>483</v>
       </c>
-      <c r="F97" s="147" t="s">
+      <c r="F97" s="131" t="s">
         <v>472</v>
       </c>
-      <c r="G97" s="147" t="s">
+      <c r="G97" s="131" t="s">
         <v>484</v>
       </c>
-      <c r="H97" s="150" t="s">
+      <c r="H97" s="132" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="99" ht="17.6" spans="1:20">
-      <c r="A99" s="227" t="s">
+      <c r="A99" s="211" t="s">
         <v>485</v>
       </c>
-      <c r="B99" s="227"/>
-      <c r="C99" s="227"/>
-      <c r="D99" s="227"/>
-      <c r="E99" s="227"/>
-      <c r="F99" s="227"/>
-      <c r="G99" s="227"/>
-      <c r="H99" s="227"/>
-      <c r="I99" s="227"/>
-      <c r="J99" s="227"/>
-      <c r="K99" s="227"/>
-      <c r="L99" s="227"/>
-      <c r="M99" s="227"/>
-      <c r="N99" s="227"/>
-      <c r="O99" s="227"/>
-      <c r="P99" s="227"/>
-      <c r="Q99" s="227"/>
-      <c r="R99" s="227"/>
-      <c r="S99" s="227"/>
-      <c r="T99" s="227"/>
+      <c r="B99" s="211"/>
+      <c r="C99" s="211"/>
+      <c r="D99" s="211"/>
+      <c r="E99" s="211"/>
+      <c r="F99" s="211"/>
+      <c r="G99" s="211"/>
+      <c r="H99" s="211"/>
+      <c r="I99" s="211"/>
+      <c r="J99" s="211"/>
+      <c r="K99" s="211"/>
+      <c r="L99" s="211"/>
+      <c r="M99" s="211"/>
+      <c r="N99" s="211"/>
+      <c r="O99" s="211"/>
+      <c r="P99" s="211"/>
+      <c r="Q99" s="211"/>
+      <c r="R99" s="211"/>
+      <c r="S99" s="211"/>
+      <c r="T99" s="211"/>
     </row>
     <row r="100" spans="1:20">
-      <c r="A100" s="182"/>
-      <c r="B100" s="182"/>
-      <c r="C100" s="182"/>
-      <c r="D100" s="182"/>
-      <c r="E100" s="182"/>
-      <c r="F100" s="182"/>
-      <c r="G100" s="182"/>
-      <c r="H100" s="182"/>
-      <c r="I100" s="182"/>
+      <c r="A100" s="168"/>
+      <c r="B100" s="168"/>
+      <c r="C100" s="168"/>
+      <c r="D100" s="168"/>
+      <c r="E100" s="168"/>
+      <c r="F100" s="168"/>
+      <c r="G100" s="168"/>
+      <c r="H100" s="168"/>
+      <c r="I100" s="168"/>
     </row>
     <row r="101" spans="1:20">
-      <c r="A101" s="228" t="s">
+      <c r="A101" s="212" t="s">
         <v>70</v>
       </c>
-      <c r="B101" s="228" t="s">
+      <c r="B101" s="212" t="s">
         <v>486</v>
       </c>
-      <c r="C101" s="228" t="s">
+      <c r="C101" s="212" t="s">
         <v>72</v>
       </c>
-      <c r="D101" s="228" t="s">
+      <c r="D101" s="212" t="s">
         <v>73</v>
       </c>
-      <c r="E101" s="228" t="s">
+      <c r="E101" s="212" t="s">
         <v>487</v>
       </c>
-      <c r="F101" s="228" t="s">
+      <c r="F101" s="212" t="s">
         <v>75</v>
       </c>
-      <c r="G101" s="228" t="s">
+      <c r="G101" s="212" t="s">
         <v>488</v>
       </c>
-      <c r="H101" s="228" t="s">
+      <c r="H101" s="212" t="s">
         <v>77</v>
       </c>
-      <c r="I101" s="228" t="s">
+      <c r="I101" s="212" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="102" ht="28" spans="1:20">
-      <c r="A102" s="226">
+      <c r="A102" s="210">
         <v>1</v>
       </c>
-      <c r="B102" s="133" t="s">
+      <c r="B102" s="122" t="s">
         <v>80</v>
       </c>
-      <c r="C102" s="133" t="s">
+      <c r="C102" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="D102" s="133" t="s">
+      <c r="D102" s="122" t="s">
         <v>81</v>
       </c>
-      <c r="E102" s="133" t="s">
+      <c r="E102" s="122" t="s">
         <v>82</v>
       </c>
-      <c r="F102" s="133" t="s">
+      <c r="F102" s="122" t="s">
         <v>83</v>
       </c>
-      <c r="G102" s="133" t="s">
+      <c r="G102" s="122" t="s">
         <v>84</v>
       </c>
-      <c r="H102" s="133" t="s">
+      <c r="H102" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="I102" s="136" t="s">
+      <c r="I102" s="125" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="103" ht="28" spans="1:20">
-      <c r="A103" s="219">
+      <c r="A103" s="203">
         <v>2</v>
       </c>
-      <c r="B103" s="138" t="s">
+      <c r="B103" s="127" t="s">
         <v>88</v>
       </c>
-      <c r="C103" s="138" t="s">
+      <c r="C103" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="D103" s="138" t="s">
+      <c r="D103" s="127" t="s">
         <v>89</v>
       </c>
-      <c r="E103" s="138" t="s">
+      <c r="E103" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="F103" s="138" t="s">
+      <c r="F103" s="127" t="s">
         <v>90</v>
       </c>
-      <c r="G103" s="138" t="s">
+      <c r="G103" s="127" t="s">
         <v>91</v>
       </c>
-      <c r="H103" s="138" t="s">
+      <c r="H103" s="127" t="s">
         <v>85</v>
       </c>
-      <c r="I103" s="141" t="s">
+      <c r="I103" s="130" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="104" ht="28" spans="1:20">
-      <c r="A104" s="219">
+      <c r="A104" s="203">
         <v>3</v>
       </c>
-      <c r="B104" s="138" t="s">
+      <c r="B104" s="127" t="s">
         <v>93</v>
       </c>
-      <c r="C104" s="138" t="s">
+      <c r="C104" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="D104" s="138" t="s">
+      <c r="D104" s="127" t="s">
         <v>94</v>
       </c>
-      <c r="E104" s="138" t="s">
+      <c r="E104" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="F104" s="138" t="s">
+      <c r="F104" s="127" t="s">
         <v>90</v>
       </c>
-      <c r="G104" s="138" t="s">
+      <c r="G104" s="127" t="s">
         <v>95</v>
       </c>
-      <c r="H104" s="138" t="s">
+      <c r="H104" s="127" t="s">
         <v>96</v>
       </c>
-      <c r="I104" s="141" t="s">
+      <c r="I104" s="130" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="105" ht="28" spans="1:20">
-      <c r="A105" s="219">
+      <c r="A105" s="203">
         <v>4</v>
       </c>
-      <c r="B105" s="138" t="s">
+      <c r="B105" s="127" t="s">
         <v>98</v>
       </c>
-      <c r="C105" s="138" t="s">
+      <c r="C105" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="D105" s="138" t="s">
+      <c r="D105" s="127" t="s">
         <v>99</v>
       </c>
-      <c r="E105" s="138" t="s">
+      <c r="E105" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="F105" s="138" t="s">
+      <c r="F105" s="127" t="s">
         <v>100</v>
       </c>
-      <c r="G105" s="138" t="s">
+      <c r="G105" s="127" t="s">
         <v>101</v>
       </c>
-      <c r="H105" s="138" t="s">
+      <c r="H105" s="127" t="s">
         <v>102</v>
       </c>
-      <c r="I105" s="141" t="s">
+      <c r="I105" s="130" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="106" ht="28" spans="1:20">
-      <c r="A106" s="219">
+      <c r="A106" s="203">
         <v>5</v>
       </c>
-      <c r="B106" s="138" t="s">
+      <c r="B106" s="127" t="s">
         <v>105</v>
       </c>
-      <c r="C106" s="138" t="s">
+      <c r="C106" s="127" t="s">
         <v>104</v>
       </c>
-      <c r="D106" s="138" t="s">
+      <c r="D106" s="127" t="s">
         <v>106</v>
       </c>
-      <c r="E106" s="138" t="s">
+      <c r="E106" s="127" t="s">
         <v>107</v>
       </c>
-      <c r="F106" s="138" t="s">
+      <c r="F106" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="G106" s="138" t="s">
+      <c r="G106" s="127" t="s">
         <v>109</v>
       </c>
-      <c r="H106" s="138" t="s">
+      <c r="H106" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="I106" s="141" t="s">
+      <c r="I106" s="130" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="107" ht="28" spans="1:20">
-      <c r="A107" s="219">
+      <c r="A107" s="203">
         <v>6</v>
       </c>
-      <c r="B107" s="138" t="s">
+      <c r="B107" s="127" t="s">
         <v>112</v>
       </c>
-      <c r="C107" s="138" t="s">
+      <c r="C107" s="127" t="s">
         <v>104</v>
       </c>
-      <c r="D107" s="138" t="s">
+      <c r="D107" s="127" t="s">
         <v>113</v>
       </c>
-      <c r="E107" s="138" t="s">
+      <c r="E107" s="127" t="s">
         <v>114</v>
       </c>
-      <c r="F107" s="138" t="s">
+      <c r="F107" s="127" t="s">
         <v>115</v>
       </c>
-      <c r="G107" s="138" t="s">
+      <c r="G107" s="127" t="s">
         <v>116</v>
       </c>
-      <c r="H107" s="138" t="s">
+      <c r="H107" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="I107" s="141" t="s">
+      <c r="I107" s="130" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="108" ht="28" spans="1:20">
-      <c r="A108" s="219">
+      <c r="A108" s="203">
         <v>7</v>
       </c>
-      <c r="B108" s="138" t="s">
+      <c r="B108" s="127" t="s">
         <v>118</v>
       </c>
-      <c r="C108" s="138" t="s">
+      <c r="C108" s="127" t="s">
         <v>117</v>
       </c>
-      <c r="D108" s="138" t="s">
+      <c r="D108" s="127" t="s">
         <v>119</v>
       </c>
-      <c r="E108" s="138" t="s">
+      <c r="E108" s="127" t="s">
         <v>120</v>
       </c>
-      <c r="F108" s="138" t="s">
+      <c r="F108" s="127" t="s">
         <v>121</v>
       </c>
-      <c r="G108" s="138" t="s">
+      <c r="G108" s="127" t="s">
         <v>122</v>
       </c>
-      <c r="H108" s="138" t="s">
+      <c r="H108" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="I108" s="141" t="s">
+      <c r="I108" s="130" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="109" ht="28" spans="1:20">
-      <c r="A109" s="219">
+      <c r="A109" s="203">
         <v>8</v>
       </c>
-      <c r="B109" s="138" t="s">
+      <c r="B109" s="127" t="s">
         <v>128</v>
       </c>
-      <c r="C109" s="138" t="s">
+      <c r="C109" s="127" t="s">
         <v>127</v>
       </c>
-      <c r="D109" s="138" t="s">
+      <c r="D109" s="127" t="s">
         <v>129</v>
       </c>
-      <c r="E109" s="138" t="s">
+      <c r="E109" s="127" t="s">
         <v>120</v>
       </c>
-      <c r="F109" s="138" t="s">
+      <c r="F109" s="127" t="s">
         <v>130</v>
       </c>
-      <c r="G109" s="138" t="s">
+      <c r="G109" s="127" t="s">
         <v>131</v>
       </c>
-      <c r="H109" s="138" t="s">
+      <c r="H109" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="I109" s="141" t="s">
+      <c r="I109" s="130" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="110" ht="28" spans="1:20">
-      <c r="A110" s="219">
+      <c r="A110" s="203">
         <v>9</v>
       </c>
-      <c r="B110" s="138" t="s">
+      <c r="B110" s="127" t="s">
         <v>135</v>
       </c>
-      <c r="C110" s="138" t="s">
+      <c r="C110" s="127" t="s">
         <v>134</v>
       </c>
-      <c r="D110" s="138" t="s">
+      <c r="D110" s="127" t="s">
         <v>136</v>
       </c>
-      <c r="E110" s="138" t="s">
+      <c r="E110" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="F110" s="138" t="s">
+      <c r="F110" s="127" t="s">
         <v>137</v>
       </c>
-      <c r="G110" s="138" t="s">
+      <c r="G110" s="127" t="s">
         <v>138</v>
       </c>
-      <c r="H110" s="138" t="s">
+      <c r="H110" s="127" t="s">
         <v>139</v>
       </c>
-      <c r="I110" s="141" t="s">
+      <c r="I110" s="130" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="111" ht="28" spans="1:20">
-      <c r="A111" s="219">
+      <c r="A111" s="203">
         <v>10</v>
       </c>
-      <c r="B111" s="138" t="s">
+      <c r="B111" s="127" t="s">
         <v>143</v>
       </c>
-      <c r="C111" s="138" t="s">
+      <c r="C111" s="127" t="s">
         <v>142</v>
       </c>
-      <c r="D111" s="138" t="s">
+      <c r="D111" s="127" t="s">
         <v>144</v>
       </c>
-      <c r="E111" s="138" t="s">
+      <c r="E111" s="127" t="s">
         <v>145</v>
       </c>
-      <c r="F111" s="138" t="s">
+      <c r="F111" s="127" t="s">
         <v>146</v>
       </c>
-      <c r="G111" s="138" t="s">
+      <c r="G111" s="127" t="s">
         <v>147</v>
       </c>
-      <c r="H111" s="138" t="s">
+      <c r="H111" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="I111" s="141" t="s">
+      <c r="I111" s="130" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="112" ht="28" spans="1:20">
-      <c r="A112" s="219">
+      <c r="A112" s="203">
         <v>11</v>
       </c>
-      <c r="B112" s="138" t="s">
+      <c r="B112" s="127" t="s">
         <v>151</v>
       </c>
-      <c r="C112" s="138" t="s">
+      <c r="C112" s="127" t="s">
         <v>150</v>
       </c>
-      <c r="D112" s="138" t="s">
+      <c r="D112" s="127" t="s">
         <v>152</v>
       </c>
-      <c r="E112" s="138" t="s">
+      <c r="E112" s="127" t="s">
         <v>153</v>
       </c>
-      <c r="F112" s="138" t="s">
+      <c r="F112" s="127" t="s">
         <v>154</v>
       </c>
-      <c r="G112" s="138" t="s">
+      <c r="G112" s="127" t="s">
         <v>155</v>
       </c>
-      <c r="H112" s="138" t="s">
+      <c r="H112" s="127" t="s">
         <v>156</v>
       </c>
-      <c r="I112" s="141" t="s">
+      <c r="I112" s="130" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="113" ht="28" spans="1:9">
-      <c r="A113" s="219">
+      <c r="A113" s="203">
         <v>12</v>
       </c>
-      <c r="B113" s="138" t="s">
+      <c r="B113" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="C113" s="138" t="s">
+      <c r="C113" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="D113" s="138" t="s">
+      <c r="D113" s="127" t="s">
         <v>161</v>
       </c>
-      <c r="E113" s="138" t="s">
+      <c r="E113" s="127" t="s">
         <v>162</v>
       </c>
-      <c r="F113" s="138" t="s">
+      <c r="F113" s="127" t="s">
         <v>163</v>
       </c>
-      <c r="G113" s="138" t="s">
+      <c r="G113" s="127" t="s">
         <v>164</v>
       </c>
-      <c r="H113" s="138" t="s">
+      <c r="H113" s="127" t="s">
         <v>165</v>
       </c>
-      <c r="I113" s="141" t="s">
+      <c r="I113" s="130" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="114" ht="28" spans="1:9">
-      <c r="A114" s="219">
+      <c r="A114" s="203">
         <v>13</v>
       </c>
-      <c r="B114" s="138" t="s">
+      <c r="B114" s="127" t="s">
         <v>168</v>
       </c>
-      <c r="C114" s="138" t="s">
+      <c r="C114" s="127" t="s">
         <v>127</v>
       </c>
-      <c r="D114" s="138" t="s">
+      <c r="D114" s="127" t="s">
         <v>169</v>
       </c>
-      <c r="E114" s="138" t="s">
+      <c r="E114" s="127" t="s">
         <v>170</v>
       </c>
-      <c r="F114" s="138" t="s">
+      <c r="F114" s="127" t="s">
         <v>171</v>
       </c>
-      <c r="G114" s="138" t="s">
+      <c r="G114" s="127" t="s">
         <v>172</v>
       </c>
-      <c r="H114" s="138" t="s">
+      <c r="H114" s="127" t="s">
         <v>173</v>
       </c>
-      <c r="I114" s="141" t="s">
+      <c r="I114" s="130" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="115" ht="41" spans="1:9">
-      <c r="A115" s="219">
+      <c r="A115" s="203">
         <v>14</v>
       </c>
-      <c r="B115" s="138" t="s">
+      <c r="B115" s="127" t="s">
         <v>490</v>
       </c>
-      <c r="C115" s="138" t="s">
+      <c r="C115" s="127" t="s">
         <v>491</v>
       </c>
-      <c r="D115" s="138" t="s">
+      <c r="D115" s="127" t="s">
         <v>492</v>
       </c>
-      <c r="E115" s="138" t="s">
+      <c r="E115" s="127" t="s">
         <v>493</v>
       </c>
-      <c r="F115" s="138" t="s">
+      <c r="F115" s="127" t="s">
         <v>171</v>
       </c>
-      <c r="G115" s="138" t="s">
+      <c r="G115" s="127" t="s">
         <v>494</v>
       </c>
-      <c r="H115" s="138" t="s">
+      <c r="H115" s="127" t="s">
         <v>439</v>
       </c>
-      <c r="I115" s="141" t="s">
+      <c r="I115" s="130" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="116" ht="28" spans="1:9">
-      <c r="A116" s="221">
+      <c r="A116" s="205">
         <v>15</v>
       </c>
-      <c r="B116" s="147" t="s">
+      <c r="B116" s="131" t="s">
         <v>495</v>
       </c>
-      <c r="C116" s="147" t="s">
+      <c r="C116" s="131" t="s">
         <v>496</v>
       </c>
-      <c r="D116" s="147" t="s">
+      <c r="D116" s="131" t="s">
         <v>497</v>
       </c>
-      <c r="E116" s="147" t="s">
+      <c r="E116" s="131" t="s">
         <v>498</v>
       </c>
-      <c r="F116" s="147" t="s">
+      <c r="F116" s="131" t="s">
         <v>499</v>
       </c>
-      <c r="G116" s="147" t="s">
+      <c r="G116" s="131" t="s">
         <v>500</v>
       </c>
-      <c r="H116" s="147" t="s">
+      <c r="H116" s="131" t="s">
         <v>419</v>
       </c>
-      <c r="I116" s="150" t="s">
+      <c r="I116" s="132" t="s">
         <v>501</v>
       </c>
     </row>
@@ -10415,14 +10369,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="E43:F43 E44:F44 E45:F45 E31:F42 E46:F47">
-      <formula1>"Required,Required for UGC stabilization,Target / fallback,Recommended,Optional"</formula1>
-    </dataValidation>
     <dataValidation type="list" sqref="E48:E60">
       <formula1>"Core complete / stabilize,Core complete / optimize,Pending,Planned,Deferred,Dropped"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="G47:G60">
       <formula1>"P0,P1,P2,P3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E31:F47">
+      <formula1>"Required,Required for UGC stabilization,Target / fallback,Recommended,Optional"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10727,7 +10681,7 @@
       <c r="D16" s="28"/>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
-      <c r="G16" s="123"/>
+      <c r="G16" s="29"/>
       <c r="H16" s="43" t="s">
         <v>515</v>
       </c>
@@ -10886,15 +10840,15 @@
       <c r="C35" s="44"/>
       <c r="D35" s="44"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="123"/>
-      <c r="G35" s="123"/>
-      <c r="H35" s="123"/>
-      <c r="I35" s="123"/>
-      <c r="J35" s="123"/>
-      <c r="K35" s="123"/>
-      <c r="L35" s="123"/>
-      <c r="M35" s="123"/>
-      <c r="N35" s="123"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="45" t="s">
@@ -11006,15 +10960,15 @@
       <c r="C45" s="52"/>
       <c r="D45" s="52"/>
       <c r="E45" s="52"/>
-      <c r="F45" s="123"/>
-      <c r="G45" s="123"/>
-      <c r="H45" s="123"/>
-      <c r="I45" s="123"/>
-      <c r="J45" s="123"/>
-      <c r="K45" s="123"/>
-      <c r="L45" s="123"/>
-      <c r="M45" s="123"/>
-      <c r="N45" s="123"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="53" t="s">
@@ -11032,15 +10986,15 @@
       <c r="E46" s="53" t="s">
         <v>567</v>
       </c>
-      <c r="F46" s="124"/>
-      <c r="G46" s="124"/>
-      <c r="H46" s="124"/>
-      <c r="I46" s="124"/>
-      <c r="J46" s="124"/>
-      <c r="K46" s="124"/>
-      <c r="L46" s="124"/>
-      <c r="M46" s="124"/>
-      <c r="N46" s="124"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="81"/>
+      <c r="M46" s="81"/>
+      <c r="N46" s="81"/>
     </row>
     <row r="47" ht="28" spans="1:14">
       <c r="A47" s="46" t="s">
@@ -11058,15 +11012,15 @@
       <c r="E47" s="47" t="s">
         <v>572</v>
       </c>
-      <c r="F47" s="124"/>
-      <c r="G47" s="124"/>
-      <c r="H47" s="124"/>
-      <c r="I47" s="124"/>
-      <c r="J47" s="124"/>
-      <c r="K47" s="124"/>
-      <c r="L47" s="124"/>
-      <c r="M47" s="124"/>
-      <c r="N47" s="124"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="81"/>
+      <c r="I47" s="81"/>
+      <c r="J47" s="81"/>
+      <c r="K47" s="81"/>
+      <c r="L47" s="81"/>
+      <c r="M47" s="81"/>
+      <c r="N47" s="81"/>
     </row>
     <row r="48" ht="28" spans="1:14">
       <c r="A48" s="48" t="s">
@@ -11084,15 +11038,15 @@
       <c r="E48" s="49" t="s">
         <v>577</v>
       </c>
-      <c r="F48" s="124"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="124"/>
-      <c r="I48" s="124"/>
-      <c r="J48" s="124"/>
-      <c r="K48" s="124"/>
-      <c r="L48" s="124"/>
-      <c r="M48" s="124"/>
-      <c r="N48" s="124"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="81"/>
+      <c r="I48" s="81"/>
+      <c r="J48" s="81"/>
+      <c r="K48" s="81"/>
+      <c r="L48" s="81"/>
+      <c r="M48" s="81"/>
+      <c r="N48" s="81"/>
     </row>
     <row r="49" ht="28" spans="1:15">
       <c r="A49" s="48" t="s">
@@ -11110,15 +11064,15 @@
       <c r="E49" s="49" t="s">
         <v>582</v>
       </c>
-      <c r="F49" s="124"/>
-      <c r="G49" s="124"/>
-      <c r="H49" s="124"/>
-      <c r="I49" s="124"/>
-      <c r="J49" s="124"/>
-      <c r="K49" s="124"/>
-      <c r="L49" s="124"/>
-      <c r="M49" s="124"/>
-      <c r="N49" s="124"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="81"/>
+      <c r="M49" s="81"/>
+      <c r="N49" s="81"/>
     </row>
     <row r="50" ht="28" spans="1:15">
       <c r="A50" s="50" t="s">
@@ -11136,37 +11090,37 @@
       <c r="E50" s="51" t="s">
         <v>587</v>
       </c>
-      <c r="F50" s="124"/>
-      <c r="G50" s="124"/>
-      <c r="H50" s="124"/>
-      <c r="I50" s="124"/>
-      <c r="J50" s="124"/>
-      <c r="K50" s="124"/>
-      <c r="L50" s="124"/>
-      <c r="M50" s="124"/>
-      <c r="N50" s="124"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="81"/>
+      <c r="M50" s="81"/>
+      <c r="N50" s="81"/>
     </row>
     <row r="51" spans="1:15">
-      <c r="F51" s="124"/>
-      <c r="G51" s="124"/>
-      <c r="H51" s="124"/>
-      <c r="I51" s="124"/>
-      <c r="J51" s="124"/>
-      <c r="K51" s="124"/>
-      <c r="L51" s="124"/>
-      <c r="M51" s="124"/>
-      <c r="N51" s="124"/>
+      <c r="F51" s="81"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="81"/>
+      <c r="I51" s="81"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="81"/>
+      <c r="L51" s="81"/>
+      <c r="M51" s="81"/>
+      <c r="N51" s="81"/>
     </row>
     <row r="52" spans="1:15">
-      <c r="F52" s="124"/>
-      <c r="G52" s="124"/>
-      <c r="H52" s="124"/>
-      <c r="I52" s="124"/>
-      <c r="J52" s="124"/>
-      <c r="K52" s="124"/>
-      <c r="L52" s="124"/>
-      <c r="M52" s="124"/>
-      <c r="N52" s="124"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
+      <c r="M52" s="81"/>
+      <c r="N52" s="81"/>
     </row>
     <row r="53" ht="17.6" spans="1:15">
       <c r="A53" s="54" t="s">
@@ -11175,16 +11129,16 @@
       <c r="B53" s="54"/>
       <c r="C53" s="54"/>
       <c r="D53" s="54"/>
-      <c r="E53" s="123"/>
-      <c r="F53" s="123"/>
-      <c r="G53" s="123"/>
-      <c r="H53" s="123"/>
-      <c r="I53" s="123"/>
-      <c r="J53" s="123"/>
-      <c r="K53" s="123"/>
-      <c r="L53" s="123"/>
-      <c r="M53" s="123"/>
-      <c r="N53" s="123"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="29"/>
+      <c r="N53" s="29"/>
     </row>
     <row r="54" spans="1:15">
       <c r="A54" s="55" t="s">
@@ -11199,15 +11153,15 @@
       <c r="D54" s="55" t="s">
         <v>590</v>
       </c>
-      <c r="F54" s="124"/>
-      <c r="G54" s="124"/>
-      <c r="H54" s="124"/>
-      <c r="I54" s="124"/>
-      <c r="J54" s="124"/>
-      <c r="K54" s="124"/>
-      <c r="L54" s="124"/>
-      <c r="M54" s="124"/>
-      <c r="N54" s="124"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
+      <c r="M54" s="81"/>
+      <c r="N54" s="81"/>
     </row>
     <row r="55" ht="109" spans="1:15">
       <c r="A55" s="56" t="s">
@@ -11222,27 +11176,27 @@
       <c r="D55" s="58" t="s">
         <v>201</v>
       </c>
-      <c r="F55" s="124"/>
-      <c r="G55" s="125"/>
-      <c r="H55" s="125"/>
-      <c r="I55" s="125"/>
-      <c r="J55" s="125"/>
-      <c r="K55" s="125"/>
-      <c r="L55" s="125"/>
-      <c r="M55" s="125"/>
-      <c r="N55" s="125"/>
-      <c r="O55" s="125"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="114"/>
+      <c r="H55" s="114"/>
+      <c r="I55" s="114"/>
+      <c r="J55" s="114"/>
+      <c r="K55" s="114"/>
+      <c r="L55" s="114"/>
+      <c r="M55" s="114"/>
+      <c r="N55" s="114"/>
+      <c r="O55" s="114"/>
     </row>
     <row r="56" spans="1:15">
-      <c r="G56" s="125"/>
-      <c r="H56" s="125"/>
-      <c r="I56" s="125"/>
-      <c r="J56" s="125"/>
-      <c r="K56" s="125"/>
-      <c r="L56" s="125"/>
-      <c r="M56" s="125"/>
-      <c r="N56" s="125"/>
-      <c r="O56" s="125"/>
+      <c r="G56" s="114"/>
+      <c r="H56" s="114"/>
+      <c r="I56" s="114"/>
+      <c r="J56" s="114"/>
+      <c r="K56" s="114"/>
+      <c r="L56" s="114"/>
+      <c r="M56" s="114"/>
+      <c r="N56" s="114"/>
+      <c r="O56" s="114"/>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" s="60" t="s">
@@ -11260,42 +11214,42 @@
       <c r="K57" s="61"/>
       <c r="L57" s="61"/>
       <c r="M57" s="61"/>
-      <c r="N57" s="62"/>
-      <c r="O57" s="125"/>
+      <c r="N57" s="61"/>
+      <c r="O57" s="114"/>
     </row>
     <row r="58" spans="1:15">
-      <c r="A58" s="126"/>
-      <c r="B58" s="126"/>
-      <c r="C58" s="126"/>
-      <c r="D58" s="126"/>
-      <c r="E58" s="126"/>
-      <c r="F58" s="126"/>
-      <c r="G58" s="65"/>
-      <c r="H58" s="65"/>
-      <c r="I58" s="65"/>
-      <c r="J58" s="65"/>
-      <c r="K58" s="65"/>
-      <c r="L58" s="65"/>
-      <c r="M58" s="65"/>
-      <c r="N58" s="66"/>
-      <c r="O58" s="125"/>
+      <c r="A58" s="115"/>
+      <c r="B58" s="115"/>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="G58" s="61"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="61"/>
+      <c r="J58" s="61"/>
+      <c r="K58" s="61"/>
+      <c r="L58" s="61"/>
+      <c r="M58" s="61"/>
+      <c r="N58" s="61"/>
+      <c r="O58" s="114"/>
     </row>
     <row r="59" spans="1:15">
-      <c r="A59" s="126"/>
-      <c r="B59" s="126"/>
-      <c r="C59" s="126"/>
-      <c r="D59" s="126"/>
-      <c r="E59" s="126"/>
-      <c r="F59" s="126"/>
-      <c r="G59" s="125"/>
-      <c r="H59" s="125"/>
-      <c r="I59" s="125"/>
-      <c r="J59" s="125"/>
-      <c r="K59" s="125"/>
-      <c r="L59" s="125"/>
-      <c r="M59" s="125"/>
-      <c r="N59" s="125"/>
-      <c r="O59" s="125"/>
+      <c r="A59" s="115"/>
+      <c r="B59" s="115"/>
+      <c r="C59" s="115"/>
+      <c r="D59" s="115"/>
+      <c r="E59" s="115"/>
+      <c r="F59" s="115"/>
+      <c r="G59" s="114"/>
+      <c r="H59" s="114"/>
+      <c r="I59" s="114"/>
+      <c r="J59" s="114"/>
+      <c r="K59" s="114"/>
+      <c r="L59" s="114"/>
+      <c r="M59" s="114"/>
+      <c r="N59" s="114"/>
+      <c r="O59" s="114"/>
     </row>
     <row r="60" ht="17.6" spans="1:15">
       <c r="A60" s="44" t="s">
@@ -11306,37 +11260,37 @@
       <c r="D60" s="44"/>
       <c r="E60" s="44"/>
       <c r="F60" s="44"/>
-      <c r="G60" s="123"/>
-      <c r="H60" s="123"/>
-      <c r="I60" s="123"/>
-      <c r="J60" s="123"/>
-      <c r="K60" s="123"/>
-      <c r="L60" s="123"/>
-      <c r="M60" s="123"/>
-      <c r="N60" s="123"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="29"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="29"/>
+      <c r="N60" s="29"/>
     </row>
     <row r="61" spans="1:15">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="67" t="s">
+      <c r="B61" s="64" t="s">
         <v>593</v>
       </c>
-      <c r="C61" s="67" t="s">
+      <c r="C61" s="64" t="s">
         <v>594</v>
       </c>
-      <c r="D61" s="67" t="s">
+      <c r="D61" s="64" t="s">
         <v>595</v>
       </c>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="64" t="s">
         <v>596</v>
       </c>
-      <c r="F61" s="67" t="s">
+      <c r="F61" s="64" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="62" ht="41" spans="1:15">
-      <c r="A62" s="68">
+      <c r="A62" s="65">
         <v>1</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -11356,7 +11310,7 @@
       </c>
     </row>
     <row r="63" ht="28" spans="1:15">
-      <c r="A63" s="69">
+      <c r="A63" s="66">
         <v>2</v>
       </c>
       <c r="B63" s="12" t="s">
@@ -11376,7 +11330,7 @@
       </c>
     </row>
     <row r="64" ht="28" spans="1:15">
-      <c r="A64" s="69">
+      <c r="A64" s="66">
         <v>3</v>
       </c>
       <c r="B64" s="12" t="s">
@@ -11396,7 +11350,7 @@
       </c>
     </row>
     <row r="65" ht="28" spans="1:14">
-      <c r="A65" s="69">
+      <c r="A65" s="66">
         <v>4</v>
       </c>
       <c r="B65" s="12" t="s">
@@ -11416,7 +11370,7 @@
       </c>
     </row>
     <row r="66" ht="28" spans="1:14">
-      <c r="A66" s="70">
+      <c r="A66" s="67">
         <v>5</v>
       </c>
       <c r="B66" s="22" t="s">
@@ -11444,37 +11398,37 @@
       <c r="D69" s="52"/>
       <c r="E69" s="52"/>
       <c r="F69" s="52"/>
-      <c r="G69" s="123"/>
-      <c r="H69" s="123"/>
-      <c r="I69" s="123"/>
-      <c r="J69" s="123"/>
-      <c r="K69" s="123"/>
-      <c r="L69" s="123"/>
-      <c r="M69" s="123"/>
-      <c r="N69" s="123"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="29"/>
+      <c r="I69" s="29"/>
+      <c r="J69" s="29"/>
+      <c r="K69" s="29"/>
+      <c r="L69" s="29"/>
+      <c r="M69" s="29"/>
+      <c r="N69" s="29"/>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" s="71" t="s">
+      <c r="A70" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="71" t="s">
+      <c r="B70" s="68" t="s">
         <v>624</v>
       </c>
-      <c r="C70" s="71" t="s">
+      <c r="C70" s="68" t="s">
         <v>625</v>
       </c>
-      <c r="D70" s="71" t="s">
+      <c r="D70" s="68" t="s">
         <v>626</v>
       </c>
-      <c r="E70" s="71" t="s">
+      <c r="E70" s="68" t="s">
         <v>627</v>
       </c>
-      <c r="F70" s="71" t="s">
+      <c r="F70" s="68" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="71" ht="28" spans="1:14">
-      <c r="A71" s="68">
+      <c r="A71" s="65">
         <v>1</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -11494,7 +11448,7 @@
       </c>
     </row>
     <row r="72" ht="28" spans="1:14">
-      <c r="A72" s="69">
+      <c r="A72" s="66">
         <v>2</v>
       </c>
       <c r="B72" s="12" t="s">
@@ -11514,7 +11468,7 @@
       </c>
     </row>
     <row r="73" ht="28" spans="1:14">
-      <c r="A73" s="69">
+      <c r="A73" s="66">
         <v>3</v>
       </c>
       <c r="B73" s="12" t="s">
@@ -11534,7 +11488,7 @@
       </c>
     </row>
     <row r="74" ht="28" spans="1:14">
-      <c r="A74" s="69">
+      <c r="A74" s="66">
         <v>4</v>
       </c>
       <c r="B74" s="12" t="s">
@@ -11554,7 +11508,7 @@
       </c>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="70">
+      <c r="A75" s="67">
         <v>5</v>
       </c>
       <c r="B75" s="22" t="s">
@@ -11574,38 +11528,38 @@
       </c>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="72" t="s">
+      <c r="A77" s="69" t="s">
         <v>654</v>
       </c>
-      <c r="B77" s="73"/>
-      <c r="C77" s="73"/>
-      <c r="D77" s="73"/>
-      <c r="E77" s="73"/>
-      <c r="F77" s="73"/>
-      <c r="G77" s="74"/>
-      <c r="H77" s="74"/>
-      <c r="I77" s="74"/>
-      <c r="J77" s="74"/>
-      <c r="K77" s="74"/>
-      <c r="L77" s="74"/>
-      <c r="M77" s="74"/>
-      <c r="N77" s="75"/>
+      <c r="B77" s="70"/>
+      <c r="C77" s="70"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
+      <c r="F77" s="70"/>
+      <c r="G77" s="71"/>
+      <c r="H77" s="71"/>
+      <c r="I77" s="71"/>
+      <c r="J77" s="71"/>
+      <c r="K77" s="71"/>
+      <c r="L77" s="71"/>
+      <c r="M77" s="71"/>
+      <c r="N77" s="71"/>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" s="76"/>
-      <c r="B78" s="77"/>
-      <c r="C78" s="77"/>
-      <c r="D78" s="77"/>
-      <c r="E78" s="77"/>
-      <c r="F78" s="77"/>
-      <c r="G78" s="78"/>
-      <c r="H78" s="78"/>
-      <c r="I78" s="78"/>
-      <c r="J78" s="78"/>
-      <c r="K78" s="78"/>
-      <c r="L78" s="78"/>
-      <c r="M78" s="78"/>
-      <c r="N78" s="79"/>
+      <c r="A78" s="72"/>
+      <c r="B78" s="73"/>
+      <c r="C78" s="73"/>
+      <c r="D78" s="73"/>
+      <c r="E78" s="73"/>
+      <c r="F78" s="73"/>
+      <c r="G78" s="71"/>
+      <c r="H78" s="71"/>
+      <c r="I78" s="71"/>
+      <c r="J78" s="71"/>
+      <c r="K78" s="71"/>
+      <c r="L78" s="71"/>
+      <c r="M78" s="71"/>
+      <c r="N78" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -11638,22 +11592,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:14">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="111" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="121"/>
-      <c r="H1" s="121"/>
-      <c r="I1" s="121"/>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="121"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:14">
       <c r="A2" s="2" t="s">
@@ -12081,7 +12035,7 @@
       <c r="C35" s="44"/>
       <c r="D35" s="44"/>
       <c r="E35" s="44"/>
-      <c r="F35" s="122"/>
+      <c r="F35" s="113"/>
       <c r="G35" s="29"/>
       <c r="H35" s="29"/>
       <c r="I35" s="29"/>
@@ -12334,30 +12288,30 @@
       <c r="D56" s="60"/>
       <c r="E56" s="60"/>
       <c r="F56" s="60"/>
-      <c r="G56" s="84"/>
+      <c r="G56" s="78"/>
       <c r="H56" s="61"/>
       <c r="I56" s="61"/>
       <c r="J56" s="61"/>
       <c r="K56" s="61"/>
       <c r="L56" s="61"/>
       <c r="M56" s="61"/>
-      <c r="N56" s="62"/>
+      <c r="N56" s="61"/>
     </row>
     <row r="57" ht="28" customHeight="1" spans="1:14">
-      <c r="A57" s="63"/>
-      <c r="B57" s="64"/>
-      <c r="C57" s="64"/>
-      <c r="D57" s="64"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="86"/>
-      <c r="H57" s="65"/>
-      <c r="I57" s="65"/>
-      <c r="J57" s="65"/>
-      <c r="K57" s="65"/>
-      <c r="L57" s="65"/>
-      <c r="M57" s="65"/>
-      <c r="N57" s="66"/>
+      <c r="A57" s="62"/>
+      <c r="B57" s="63"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="63"/>
+      <c r="G57" s="80"/>
+      <c r="H57" s="61"/>
+      <c r="I57" s="61"/>
+      <c r="J57" s="61"/>
+      <c r="K57" s="61"/>
+      <c r="L57" s="61"/>
+      <c r="M57" s="61"/>
+      <c r="N57" s="61"/>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:14">
       <c r="A59" s="44" t="s">
@@ -12378,27 +12332,27 @@
       <c r="N59" s="29"/>
     </row>
     <row r="60" ht="34" customHeight="1" spans="1:14">
-      <c r="A60" s="67" t="s">
+      <c r="A60" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="67" t="s">
+      <c r="B60" s="64" t="s">
         <v>593</v>
       </c>
-      <c r="C60" s="67" t="s">
+      <c r="C60" s="64" t="s">
         <v>594</v>
       </c>
-      <c r="D60" s="67" t="s">
+      <c r="D60" s="64" t="s">
         <v>595</v>
       </c>
-      <c r="E60" s="67" t="s">
+      <c r="E60" s="64" t="s">
         <v>596</v>
       </c>
-      <c r="F60" s="67" t="s">
+      <c r="F60" s="64" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="61" ht="64" customHeight="1" spans="1:14">
-      <c r="A61" s="68">
+      <c r="A61" s="65">
         <v>1</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -12418,7 +12372,7 @@
       </c>
     </row>
     <row r="62" ht="64" customHeight="1" spans="1:14">
-      <c r="A62" s="69">
+      <c r="A62" s="66">
         <v>2</v>
       </c>
       <c r="B62" s="12" t="s">
@@ -12438,7 +12392,7 @@
       </c>
     </row>
     <row r="63" ht="64" customHeight="1" spans="1:14">
-      <c r="A63" s="69">
+      <c r="A63" s="66">
         <v>3</v>
       </c>
       <c r="B63" s="12" t="s">
@@ -12458,7 +12412,7 @@
       </c>
     </row>
     <row r="64" ht="64" customHeight="1" spans="1:14">
-      <c r="A64" s="70">
+      <c r="A64" s="67">
         <v>4</v>
       </c>
       <c r="B64" s="22" t="s">
@@ -12496,27 +12450,27 @@
       <c r="N67" s="29"/>
     </row>
     <row r="68" ht="34" customHeight="1" spans="1:14">
-      <c r="A68" s="71" t="s">
+      <c r="A68" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="71" t="s">
+      <c r="B68" s="68" t="s">
         <v>624</v>
       </c>
-      <c r="C68" s="71" t="s">
+      <c r="C68" s="68" t="s">
         <v>625</v>
       </c>
-      <c r="D68" s="71" t="s">
+      <c r="D68" s="68" t="s">
         <v>626</v>
       </c>
-      <c r="E68" s="71" t="s">
+      <c r="E68" s="68" t="s">
         <v>627</v>
       </c>
-      <c r="F68" s="71" t="s">
+      <c r="F68" s="68" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="69" ht="64" customHeight="1" spans="1:14">
-      <c r="A69" s="68">
+      <c r="A69" s="65">
         <v>1</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -12536,7 +12490,7 @@
       </c>
     </row>
     <row r="70" ht="64" customHeight="1" spans="1:14">
-      <c r="A70" s="69">
+      <c r="A70" s="66">
         <v>2</v>
       </c>
       <c r="B70" s="12" t="s">
@@ -12556,7 +12510,7 @@
       </c>
     </row>
     <row r="71" ht="64" customHeight="1" spans="1:14">
-      <c r="A71" s="69">
+      <c r="A71" s="66">
         <v>3</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -12576,7 +12530,7 @@
       </c>
     </row>
     <row r="72" ht="64" customHeight="1" spans="1:14">
-      <c r="A72" s="70">
+      <c r="A72" s="67">
         <v>4</v>
       </c>
       <c r="B72" s="22" t="s">
@@ -12596,38 +12550,38 @@
       </c>
     </row>
     <row r="74" ht="30" customHeight="1" spans="1:14">
-      <c r="A74" s="72" t="s">
+      <c r="A74" s="69" t="s">
         <v>654</v>
       </c>
-      <c r="B74" s="73"/>
-      <c r="C74" s="73"/>
-      <c r="D74" s="73"/>
-      <c r="E74" s="73"/>
-      <c r="F74" s="73"/>
-      <c r="G74" s="115"/>
-      <c r="H74" s="74"/>
-      <c r="I74" s="74"/>
-      <c r="J74" s="74"/>
-      <c r="K74" s="74"/>
-      <c r="L74" s="74"/>
-      <c r="M74" s="74"/>
-      <c r="N74" s="75"/>
+      <c r="B74" s="70"/>
+      <c r="C74" s="70"/>
+      <c r="D74" s="70"/>
+      <c r="E74" s="70"/>
+      <c r="F74" s="70"/>
+      <c r="G74" s="106"/>
+      <c r="H74" s="71"/>
+      <c r="I74" s="71"/>
+      <c r="J74" s="71"/>
+      <c r="K74" s="71"/>
+      <c r="L74" s="71"/>
+      <c r="M74" s="71"/>
+      <c r="N74" s="71"/>
     </row>
     <row r="75" ht="30" customHeight="1" spans="1:14">
-      <c r="A75" s="76"/>
-      <c r="B75" s="77"/>
-      <c r="C75" s="77"/>
-      <c r="D75" s="77"/>
-      <c r="E75" s="77"/>
-      <c r="F75" s="77"/>
-      <c r="G75" s="118"/>
-      <c r="H75" s="78"/>
-      <c r="I75" s="78"/>
-      <c r="J75" s="78"/>
-      <c r="K75" s="78"/>
-      <c r="L75" s="78"/>
-      <c r="M75" s="78"/>
-      <c r="N75" s="79"/>
+      <c r="A75" s="72"/>
+      <c r="B75" s="73"/>
+      <c r="C75" s="73"/>
+      <c r="D75" s="73"/>
+      <c r="E75" s="73"/>
+      <c r="F75" s="73"/>
+      <c r="G75" s="109"/>
+      <c r="H75" s="71"/>
+      <c r="I75" s="71"/>
+      <c r="J75" s="71"/>
+      <c r="K75" s="71"/>
+      <c r="L75" s="71"/>
+      <c r="M75" s="71"/>
+      <c r="N75" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12648,33 +12602,33 @@
   <dimension ref="A1:N74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13" style="96" customWidth="1"/>
-    <col min="2" max="2" width="25" style="96" customWidth="1"/>
-    <col min="3" max="4" width="31" style="96" customWidth="1"/>
-    <col min="5" max="5" width="29" style="96" customWidth="1"/>
-    <col min="6" max="6" width="23" style="96" customWidth="1"/>
-    <col min="7" max="7" width="3" style="96" customWidth="1"/>
-    <col min="8" max="14" width="17" style="96" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="96"/>
+    <col min="1" max="1" width="13" style="87" customWidth="1"/>
+    <col min="2" max="2" width="25" style="87" customWidth="1"/>
+    <col min="3" max="4" width="31" style="87" customWidth="1"/>
+    <col min="5" max="5" width="29" style="87" customWidth="1"/>
+    <col min="6" max="6" width="23" style="87" customWidth="1"/>
+    <col min="7" max="7" width="3" style="87" customWidth="1"/>
+    <col min="8" max="14" width="17" style="87" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="87"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.2" spans="1:14">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="88" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
@@ -12695,14 +12649,14 @@
       <c r="N2" s="2"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="89" t="s">
         <v>125</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100" t="s">
+      <c r="C4" s="90"/>
+      <c r="D4" s="91" t="s">
         <v>503</v>
       </c>
       <c r="E4" s="7"/>
@@ -12718,14 +12672,14 @@
       <c r="N4" s="10"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="101" t="s">
+      <c r="A5" s="92" t="s">
         <v>178</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="103" t="s">
+      <c r="C5" s="93"/>
+      <c r="D5" s="94" t="s">
         <v>505</v>
       </c>
       <c r="E5" s="15" t="str">
@@ -12742,14 +12696,14 @@
       <c r="N5" s="18"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="101" t="s">
+      <c r="A6" s="92" t="s">
         <v>179</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="C6" s="102"/>
-      <c r="D6" s="103" t="s">
+      <c r="C6" s="93"/>
+      <c r="D6" s="94" t="s">
         <v>506</v>
       </c>
       <c r="E6" s="15" t="str">
@@ -12766,14 +12720,14 @@
       <c r="N6" s="18"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="92" t="s">
         <v>182</v>
       </c>
       <c r="B7" s="19">
         <v>46247</v>
       </c>
-      <c r="C7" s="102"/>
-      <c r="D7" s="103" t="s">
+      <c r="C7" s="93"/>
+      <c r="D7" s="94" t="s">
         <v>507</v>
       </c>
       <c r="E7" s="15" t="str">
@@ -12790,12 +12744,12 @@
       <c r="N7" s="18"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="92" t="s">
         <v>183</v>
       </c>
       <c r="B8" s="19"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="103" t="s">
+      <c r="C8" s="93"/>
+      <c r="D8" s="94" t="s">
         <v>508</v>
       </c>
       <c r="E8" s="15" t="str">
@@ -12812,15 +12766,15 @@
       <c r="N8" s="18"/>
     </row>
     <row r="9" ht="28" spans="1:14">
-      <c r="A9" s="101" t="s">
+      <c r="A9" s="92" t="s">
         <v>189</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="104"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="95"/>
       <c r="G9" s="16"/>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
@@ -12831,15 +12785,15 @@
       <c r="N9" s="18"/>
     </row>
     <row r="10" ht="28" spans="1:14">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="92" t="s">
         <v>185</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>744</v>
       </c>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="104"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="95"/>
       <c r="G10" s="16"/>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
@@ -12850,15 +12804,15 @@
       <c r="N10" s="18"/>
     </row>
     <row r="11" ht="28" spans="1:14">
-      <c r="A11" s="101" t="s">
+      <c r="A11" s="92" t="s">
         <v>510</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="104"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="95"/>
       <c r="G11" s="16"/>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
@@ -12869,15 +12823,15 @@
       <c r="N11" s="18"/>
     </row>
     <row r="12" ht="28" spans="1:14">
-      <c r="A12" s="101" t="s">
+      <c r="A12" s="92" t="s">
         <v>511</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>745</v>
       </c>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="104"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="95"/>
       <c r="G12" s="16"/>
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
@@ -12888,15 +12842,15 @@
       <c r="N12" s="18"/>
     </row>
     <row r="13" ht="28" spans="1:14">
-      <c r="A13" s="101" t="s">
+      <c r="A13" s="92" t="s">
         <v>513</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="104"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="95"/>
       <c r="G13" s="16"/>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -12907,15 +12861,15 @@
       <c r="N13" s="18"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="105" t="s">
+      <c r="A14" s="96" t="s">
         <v>190</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="C14" s="106"/>
-      <c r="D14" s="106"/>
-      <c r="E14" s="107"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="97"/>
+      <c r="E14" s="98"/>
       <c r="G14" s="25"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
@@ -12926,22 +12880,22 @@
       <c r="N14" s="27"/>
     </row>
     <row r="16" ht="17.6" spans="1:14">
-      <c r="A16" s="108" t="s">
+      <c r="A16" s="99" t="s">
         <v>514</v>
       </c>
-      <c r="B16" s="108"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="108"/>
-      <c r="I16" s="108"/>
-      <c r="J16" s="108"/>
-      <c r="K16" s="108"/>
-      <c r="L16" s="108"/>
-      <c r="M16" s="108"/>
-      <c r="N16" s="108"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="99"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="99"/>
+      <c r="I16" s="99"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="99"/>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="30" t="s">
@@ -13095,22 +13049,22 @@
       <c r="N32" s="43"/>
     </row>
     <row r="35" ht="17.6" spans="1:14">
-      <c r="A35" s="109" t="s">
+      <c r="A35" s="100" t="s">
         <v>535</v>
       </c>
-      <c r="B35" s="109"/>
-      <c r="C35" s="109"/>
-      <c r="D35" s="109"/>
-      <c r="E35" s="109"/>
-      <c r="F35" s="109"/>
-      <c r="G35" s="109"/>
-      <c r="H35" s="109"/>
-      <c r="I35" s="109"/>
-      <c r="J35" s="109"/>
-      <c r="K35" s="109"/>
-      <c r="L35" s="109"/>
-      <c r="M35" s="109"/>
-      <c r="N35" s="109"/>
+      <c r="B35" s="100"/>
+      <c r="C35" s="100"/>
+      <c r="D35" s="100"/>
+      <c r="E35" s="100"/>
+      <c r="F35" s="100"/>
+      <c r="G35" s="100"/>
+      <c r="H35" s="100"/>
+      <c r="I35" s="100"/>
+      <c r="J35" s="100"/>
+      <c r="K35" s="100"/>
+      <c r="L35" s="100"/>
+      <c r="M35" s="100"/>
+      <c r="N35" s="100"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="45" t="s">
@@ -13215,22 +13169,22 @@
       </c>
     </row>
     <row r="45" ht="17.6" spans="1:14">
-      <c r="A45" s="110" t="s">
+      <c r="A45" s="101" t="s">
         <v>562</v>
       </c>
-      <c r="B45" s="110"/>
-      <c r="C45" s="110"/>
-      <c r="D45" s="110"/>
-      <c r="E45" s="110"/>
-      <c r="F45" s="110"/>
-      <c r="G45" s="110"/>
-      <c r="H45" s="110"/>
-      <c r="I45" s="110"/>
-      <c r="J45" s="110"/>
-      <c r="K45" s="110"/>
-      <c r="L45" s="110"/>
-      <c r="M45" s="110"/>
-      <c r="N45" s="110"/>
+      <c r="B45" s="101"/>
+      <c r="C45" s="101"/>
+      <c r="D45" s="101"/>
+      <c r="E45" s="101"/>
+      <c r="F45" s="101"/>
+      <c r="G45" s="101"/>
+      <c r="H45" s="101"/>
+      <c r="I45" s="101"/>
+      <c r="J45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="101"/>
+      <c r="M45" s="101"/>
+      <c r="N45" s="101"/>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="53" t="s">
@@ -13301,22 +13255,22 @@
       </c>
     </row>
     <row r="52" ht="17.6" spans="1:14">
-      <c r="A52" s="111" t="s">
+      <c r="A52" s="102" t="s">
         <v>588</v>
       </c>
-      <c r="B52" s="111"/>
-      <c r="C52" s="111"/>
-      <c r="D52" s="111"/>
-      <c r="E52" s="111"/>
-      <c r="F52" s="111"/>
-      <c r="G52" s="111"/>
-      <c r="H52" s="111"/>
-      <c r="I52" s="111"/>
-      <c r="J52" s="111"/>
-      <c r="K52" s="111"/>
-      <c r="L52" s="111"/>
-      <c r="M52" s="111"/>
-      <c r="N52" s="111"/>
+      <c r="B52" s="102"/>
+      <c r="C52" s="102"/>
+      <c r="D52" s="102"/>
+      <c r="E52" s="102"/>
+      <c r="F52" s="102"/>
+      <c r="G52" s="102"/>
+      <c r="H52" s="102"/>
+      <c r="I52" s="102"/>
+      <c r="J52" s="102"/>
+      <c r="K52" s="102"/>
+      <c r="L52" s="102"/>
+      <c r="M52" s="102"/>
+      <c r="N52" s="102"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="55" t="s">
@@ -13347,79 +13301,79 @@
       </c>
     </row>
     <row r="56" spans="1:14">
-      <c r="A56" s="83" t="s">
+      <c r="A56" s="77" t="s">
         <v>591</v>
       </c>
-      <c r="B56" s="84"/>
-      <c r="C56" s="84"/>
-      <c r="D56" s="84"/>
-      <c r="E56" s="84"/>
-      <c r="F56" s="84"/>
-      <c r="G56" s="84"/>
-      <c r="H56" s="84"/>
-      <c r="I56" s="84"/>
-      <c r="J56" s="84"/>
-      <c r="K56" s="84"/>
-      <c r="L56" s="84"/>
-      <c r="M56" s="84"/>
-      <c r="N56" s="112"/>
+      <c r="B56" s="78"/>
+      <c r="C56" s="78"/>
+      <c r="D56" s="78"/>
+      <c r="E56" s="78"/>
+      <c r="F56" s="78"/>
+      <c r="G56" s="78"/>
+      <c r="H56" s="78"/>
+      <c r="I56" s="78"/>
+      <c r="J56" s="78"/>
+      <c r="K56" s="78"/>
+      <c r="L56" s="78"/>
+      <c r="M56" s="78"/>
+      <c r="N56" s="103"/>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="85"/>
-      <c r="B57" s="86"/>
-      <c r="C57" s="86"/>
-      <c r="D57" s="86"/>
-      <c r="E57" s="86"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
-      <c r="H57" s="86"/>
-      <c r="I57" s="86"/>
-      <c r="J57" s="86"/>
-      <c r="K57" s="86"/>
-      <c r="L57" s="86"/>
-      <c r="M57" s="86"/>
-      <c r="N57" s="113"/>
+      <c r="A57" s="79"/>
+      <c r="B57" s="80"/>
+      <c r="C57" s="80"/>
+      <c r="D57" s="80"/>
+      <c r="E57" s="80"/>
+      <c r="F57" s="80"/>
+      <c r="G57" s="80"/>
+      <c r="H57" s="80"/>
+      <c r="I57" s="80"/>
+      <c r="J57" s="80"/>
+      <c r="K57" s="80"/>
+      <c r="L57" s="80"/>
+      <c r="M57" s="80"/>
+      <c r="N57" s="104"/>
     </row>
     <row r="59" ht="17.6" spans="1:14">
-      <c r="A59" s="109" t="s">
+      <c r="A59" s="100" t="s">
         <v>592</v>
       </c>
-      <c r="B59" s="109"/>
-      <c r="C59" s="109"/>
-      <c r="D59" s="109"/>
-      <c r="E59" s="109"/>
-      <c r="F59" s="109"/>
-      <c r="G59" s="109"/>
-      <c r="H59" s="109"/>
-      <c r="I59" s="109"/>
-      <c r="J59" s="109"/>
-      <c r="K59" s="109"/>
-      <c r="L59" s="109"/>
-      <c r="M59" s="109"/>
-      <c r="N59" s="109"/>
+      <c r="B59" s="100"/>
+      <c r="C59" s="100"/>
+      <c r="D59" s="100"/>
+      <c r="E59" s="100"/>
+      <c r="F59" s="100"/>
+      <c r="G59" s="100"/>
+      <c r="H59" s="100"/>
+      <c r="I59" s="100"/>
+      <c r="J59" s="100"/>
+      <c r="K59" s="100"/>
+      <c r="L59" s="100"/>
+      <c r="M59" s="100"/>
+      <c r="N59" s="100"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="67" t="s">
+      <c r="A60" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="67" t="s">
+      <c r="B60" s="64" t="s">
         <v>593</v>
       </c>
-      <c r="C60" s="67" t="s">
+      <c r="C60" s="64" t="s">
         <v>594</v>
       </c>
-      <c r="D60" s="67" t="s">
+      <c r="D60" s="64" t="s">
         <v>595</v>
       </c>
-      <c r="E60" s="67" t="s">
+      <c r="E60" s="64" t="s">
         <v>596</v>
       </c>
-      <c r="F60" s="67" t="s">
+      <c r="F60" s="64" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="61" ht="28" spans="1:14">
-      <c r="A61" s="68">
+      <c r="A61" s="65">
         <v>1</v>
       </c>
       <c r="B61" s="4" t="s">
@@ -13439,7 +13393,7 @@
       </c>
     </row>
     <row r="62" ht="28" spans="1:14">
-      <c r="A62" s="69">
+      <c r="A62" s="66">
         <v>2</v>
       </c>
       <c r="B62" s="12" t="s">
@@ -13459,7 +13413,7 @@
       </c>
     </row>
     <row r="63" ht="28" spans="1:14">
-      <c r="A63" s="69">
+      <c r="A63" s="66">
         <v>3</v>
       </c>
       <c r="B63" s="12" t="s">
@@ -13479,7 +13433,7 @@
       </c>
     </row>
     <row r="64" ht="28" spans="1:14">
-      <c r="A64" s="70">
+      <c r="A64" s="67">
         <v>4</v>
       </c>
       <c r="B64" s="22" t="s">
@@ -13499,45 +13453,45 @@
       </c>
     </row>
     <row r="67" ht="17.6" spans="1:14">
-      <c r="A67" s="110" t="s">
+      <c r="A67" s="101" t="s">
         <v>623</v>
       </c>
-      <c r="B67" s="110"/>
-      <c r="C67" s="110"/>
-      <c r="D67" s="110"/>
-      <c r="E67" s="110"/>
-      <c r="F67" s="110"/>
-      <c r="G67" s="110"/>
-      <c r="H67" s="110"/>
-      <c r="I67" s="110"/>
-      <c r="J67" s="110"/>
-      <c r="K67" s="110"/>
-      <c r="L67" s="110"/>
-      <c r="M67" s="110"/>
-      <c r="N67" s="110"/>
+      <c r="B67" s="101"/>
+      <c r="C67" s="101"/>
+      <c r="D67" s="101"/>
+      <c r="E67" s="101"/>
+      <c r="F67" s="101"/>
+      <c r="G67" s="101"/>
+      <c r="H67" s="101"/>
+      <c r="I67" s="101"/>
+      <c r="J67" s="101"/>
+      <c r="K67" s="101"/>
+      <c r="L67" s="101"/>
+      <c r="M67" s="101"/>
+      <c r="N67" s="101"/>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="71" t="s">
+      <c r="A68" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="71" t="s">
+      <c r="B68" s="68" t="s">
         <v>624</v>
       </c>
-      <c r="C68" s="71" t="s">
+      <c r="C68" s="68" t="s">
         <v>625</v>
       </c>
-      <c r="D68" s="71" t="s">
+      <c r="D68" s="68" t="s">
         <v>626</v>
       </c>
-      <c r="E68" s="71" t="s">
+      <c r="E68" s="68" t="s">
         <v>627</v>
       </c>
-      <c r="F68" s="71" t="s">
+      <c r="F68" s="68" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="69" ht="28" spans="1:14">
-      <c r="A69" s="68">
+      <c r="A69" s="65">
         <v>1</v>
       </c>
       <c r="B69" s="4" t="s">
@@ -13557,7 +13511,7 @@
       </c>
     </row>
     <row r="70" ht="28" spans="1:14">
-      <c r="A70" s="69">
+      <c r="A70" s="66">
         <v>2</v>
       </c>
       <c r="B70" s="12" t="s">
@@ -13577,7 +13531,7 @@
       </c>
     </row>
     <row r="71" ht="28" spans="1:14">
-      <c r="A71" s="70">
+      <c r="A71" s="67">
         <v>3</v>
       </c>
       <c r="B71" s="22" t="s">
@@ -13597,38 +13551,38 @@
       </c>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" s="114" t="s">
+      <c r="A73" s="105" t="s">
         <v>654</v>
       </c>
-      <c r="B73" s="115"/>
-      <c r="C73" s="115"/>
-      <c r="D73" s="115"/>
-      <c r="E73" s="115"/>
-      <c r="F73" s="115"/>
-      <c r="G73" s="115"/>
-      <c r="H73" s="115"/>
-      <c r="I73" s="115"/>
-      <c r="J73" s="115"/>
-      <c r="K73" s="115"/>
-      <c r="L73" s="115"/>
-      <c r="M73" s="115"/>
-      <c r="N73" s="116"/>
+      <c r="B73" s="106"/>
+      <c r="C73" s="106"/>
+      <c r="D73" s="106"/>
+      <c r="E73" s="106"/>
+      <c r="F73" s="106"/>
+      <c r="G73" s="106"/>
+      <c r="H73" s="106"/>
+      <c r="I73" s="106"/>
+      <c r="J73" s="106"/>
+      <c r="K73" s="106"/>
+      <c r="L73" s="106"/>
+      <c r="M73" s="106"/>
+      <c r="N73" s="107"/>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="117"/>
-      <c r="B74" s="118"/>
-      <c r="C74" s="118"/>
-      <c r="D74" s="118"/>
-      <c r="E74" s="118"/>
-      <c r="F74" s="118"/>
-      <c r="G74" s="118"/>
-      <c r="H74" s="118"/>
-      <c r="I74" s="118"/>
-      <c r="J74" s="118"/>
-      <c r="K74" s="118"/>
-      <c r="L74" s="118"/>
-      <c r="M74" s="118"/>
-      <c r="N74" s="119"/>
+      <c r="A74" s="108"/>
+      <c r="B74" s="109"/>
+      <c r="C74" s="109"/>
+      <c r="D74" s="109"/>
+      <c r="E74" s="109"/>
+      <c r="F74" s="109"/>
+      <c r="G74" s="109"/>
+      <c r="H74" s="109"/>
+      <c r="I74" s="109"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="109"/>
+      <c r="L74" s="109"/>
+      <c r="M74" s="109"/>
+      <c r="N74" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -14052,22 +14006,22 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="80">
+      <c r="A22" s="74">
         <v>5</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="75" t="s">
         <v>823</v>
       </c>
-      <c r="C22" s="81" t="s">
+      <c r="C22" s="75" t="s">
         <v>527</v>
       </c>
-      <c r="D22" s="81" t="s">
+      <c r="D22" s="75" t="s">
         <v>388</v>
       </c>
-      <c r="E22" s="81" t="s">
+      <c r="E22" s="75" t="s">
         <v>533</v>
       </c>
-      <c r="F22" s="82" t="s">
+      <c r="F22" s="76" t="s">
         <v>534</v>
       </c>
     </row>
@@ -14317,15 +14271,15 @@
         <v>851</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="83" t="s">
+    <row r="55" ht="204" spans="1:14">
+      <c r="A55" s="77" t="s">
         <v>591</v>
       </c>
-      <c r="B55" s="84"/>
-      <c r="C55" s="84"/>
-      <c r="D55" s="84"/>
-      <c r="E55" s="84"/>
-      <c r="F55" s="84"/>
+      <c r="B55" s="78"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="78"/>
+      <c r="E55" s="78"/>
+      <c r="F55" s="78"/>
       <c r="G55" s="61"/>
       <c r="H55" s="61"/>
       <c r="I55" s="61"/>
@@ -14333,23 +14287,23 @@
       <c r="K55" s="61"/>
       <c r="L55" s="61"/>
       <c r="M55" s="61"/>
-      <c r="N55" s="62"/>
+      <c r="N55" s="61"/>
     </row>
     <row r="56" spans="1:14">
-      <c r="A56" s="85"/>
-      <c r="B56" s="86"/>
-      <c r="C56" s="86"/>
-      <c r="D56" s="86"/>
-      <c r="E56" s="86"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="65"/>
-      <c r="H56" s="65"/>
-      <c r="I56" s="65"/>
-      <c r="J56" s="65"/>
-      <c r="K56" s="65"/>
-      <c r="L56" s="65"/>
-      <c r="M56" s="65"/>
-      <c r="N56" s="66"/>
+      <c r="A56" s="79"/>
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="61"/>
+      <c r="H56" s="61"/>
+      <c r="I56" s="61"/>
+      <c r="J56" s="61"/>
+      <c r="K56" s="61"/>
+      <c r="L56" s="61"/>
+      <c r="M56" s="61"/>
+      <c r="N56" s="61"/>
     </row>
     <row r="58" ht="17.6" spans="1:14">
       <c r="A58" s="44" t="s">
@@ -14370,35 +14324,35 @@
       <c r="N58" s="29"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="67" t="s">
+      <c r="A59" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B59" s="67" t="s">
+      <c r="B59" s="64" t="s">
         <v>593</v>
       </c>
-      <c r="C59" s="67" t="s">
+      <c r="C59" s="64" t="s">
         <v>594</v>
       </c>
-      <c r="D59" s="67" t="s">
+      <c r="D59" s="64" t="s">
         <v>595</v>
       </c>
-      <c r="E59" s="67" t="s">
+      <c r="E59" s="64" t="s">
         <v>596</v>
       </c>
-      <c r="F59" s="67" t="s">
+      <c r="F59" s="64" t="s">
         <v>597</v>
       </c>
-      <c r="G59" s="87"/>
-      <c r="H59" s="87"/>
-      <c r="I59" s="87"/>
-      <c r="J59" s="87"/>
-      <c r="K59" s="87"/>
-      <c r="L59" s="87"/>
-      <c r="M59" s="87"/>
-      <c r="N59" s="87"/>
+      <c r="G59" s="81"/>
+      <c r="H59" s="81"/>
+      <c r="I59" s="81"/>
+      <c r="J59" s="81"/>
+      <c r="K59" s="81"/>
+      <c r="L59" s="81"/>
+      <c r="M59" s="81"/>
+      <c r="N59" s="81"/>
     </row>
     <row r="60" ht="28" spans="1:14">
-      <c r="A60" s="68">
+      <c r="A60" s="65">
         <v>1</v>
       </c>
       <c r="B60" s="4" t="s">
@@ -14418,7 +14372,7 @@
       </c>
     </row>
     <row r="61" ht="28" spans="1:14">
-      <c r="A61" s="69">
+      <c r="A61" s="66">
         <v>2</v>
       </c>
       <c r="B61" s="12" t="s">
@@ -14438,7 +14392,7 @@
       </c>
     </row>
     <row r="62" ht="28" spans="1:14">
-      <c r="A62" s="70">
+      <c r="A62" s="67">
         <v>3</v>
       </c>
       <c r="B62" s="22" t="s">
@@ -14476,27 +14430,27 @@
       <c r="N65" s="29"/>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="71" t="s">
+      <c r="A66" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="71" t="s">
+      <c r="B66" s="68" t="s">
         <v>624</v>
       </c>
-      <c r="C66" s="71" t="s">
+      <c r="C66" s="68" t="s">
         <v>625</v>
       </c>
-      <c r="D66" s="71" t="s">
+      <c r="D66" s="68" t="s">
         <v>626</v>
       </c>
-      <c r="E66" s="71" t="s">
+      <c r="E66" s="68" t="s">
         <v>627</v>
       </c>
-      <c r="F66" s="71" t="s">
+      <c r="F66" s="68" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="67" ht="28" spans="1:14">
-      <c r="A67" s="68">
+      <c r="A67" s="65">
         <v>1</v>
       </c>
       <c r="B67" s="4" t="s">
@@ -14516,7 +14470,7 @@
       </c>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="69">
+      <c r="A68" s="66">
         <v>2</v>
       </c>
       <c r="B68" s="12" t="s">
@@ -14536,7 +14490,7 @@
       </c>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="70">
+      <c r="A69" s="67">
         <v>3</v>
       </c>
       <c r="B69" s="22" t="s">
@@ -14556,38 +14510,38 @@
       </c>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="88" t="s">
+      <c r="A71" s="82" t="s">
         <v>654</v>
       </c>
-      <c r="B71" s="89"/>
-      <c r="C71" s="89"/>
-      <c r="D71" s="89"/>
-      <c r="E71" s="89"/>
-      <c r="F71" s="89"/>
-      <c r="G71" s="89"/>
-      <c r="H71" s="90"/>
-      <c r="I71" s="90"/>
-      <c r="J71" s="90"/>
-      <c r="K71" s="90"/>
-      <c r="L71" s="90"/>
-      <c r="M71" s="90"/>
-      <c r="N71" s="91"/>
+      <c r="B71" s="83"/>
+      <c r="C71" s="83"/>
+      <c r="D71" s="83"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="83"/>
+      <c r="G71" s="83"/>
+      <c r="H71" s="84"/>
+      <c r="I71" s="84"/>
+      <c r="J71" s="84"/>
+      <c r="K71" s="84"/>
+      <c r="L71" s="84"/>
+      <c r="M71" s="84"/>
+      <c r="N71" s="84"/>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="92"/>
-      <c r="B72" s="93"/>
-      <c r="C72" s="93"/>
-      <c r="D72" s="93"/>
-      <c r="E72" s="93"/>
-      <c r="F72" s="93"/>
-      <c r="G72" s="93"/>
-      <c r="H72" s="94"/>
-      <c r="I72" s="94"/>
-      <c r="J72" s="94"/>
-      <c r="K72" s="94"/>
-      <c r="L72" s="94"/>
-      <c r="M72" s="94"/>
-      <c r="N72" s="95"/>
+      <c r="A72" s="85"/>
+      <c r="B72" s="86"/>
+      <c r="C72" s="86"/>
+      <c r="D72" s="86"/>
+      <c r="E72" s="86"/>
+      <c r="F72" s="86"/>
+      <c r="G72" s="86"/>
+      <c r="H72" s="84"/>
+      <c r="I72" s="84"/>
+      <c r="J72" s="84"/>
+      <c r="K72" s="84"/>
+      <c r="L72" s="84"/>
+      <c r="M72" s="84"/>
+      <c r="N72" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -14997,22 +14951,22 @@
       </c>
     </row>
     <row r="22" ht="32" customHeight="1" spans="1:14">
-      <c r="A22" s="80">
+      <c r="A22" s="74">
         <v>5</v>
       </c>
-      <c r="B22" s="81" t="s">
+      <c r="B22" s="75" t="s">
         <v>886</v>
       </c>
-      <c r="C22" s="81" t="s">
+      <c r="C22" s="75" t="s">
         <v>527</v>
       </c>
-      <c r="D22" s="81" t="s">
+      <c r="D22" s="75" t="s">
         <v>431</v>
       </c>
-      <c r="E22" s="81" t="s">
+      <c r="E22" s="75" t="s">
         <v>533</v>
       </c>
-      <c r="F22" s="82" t="s">
+      <c r="F22" s="76" t="s">
         <v>534</v>
       </c>
     </row>
@@ -15312,23 +15266,23 @@
       <c r="K57" s="61"/>
       <c r="L57" s="61"/>
       <c r="M57" s="61"/>
-      <c r="N57" s="62"/>
+      <c r="N57" s="61"/>
     </row>
     <row r="58" ht="28" customHeight="1" spans="1:14">
-      <c r="A58" s="63"/>
-      <c r="B58" s="64"/>
-      <c r="C58" s="64"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="65"/>
-      <c r="H58" s="65"/>
-      <c r="I58" s="65"/>
-      <c r="J58" s="65"/>
-      <c r="K58" s="65"/>
-      <c r="L58" s="65"/>
-      <c r="M58" s="65"/>
-      <c r="N58" s="66"/>
+      <c r="A58" s="62"/>
+      <c r="B58" s="63"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="61"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="61"/>
+      <c r="J58" s="61"/>
+      <c r="K58" s="61"/>
+      <c r="L58" s="61"/>
+      <c r="M58" s="61"/>
+      <c r="N58" s="61"/>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:14">
       <c r="A60" s="44" t="s">
@@ -15349,27 +15303,27 @@
       <c r="N60" s="29"/>
     </row>
     <row r="61" ht="34" customHeight="1" spans="1:14">
-      <c r="A61" s="67" t="s">
+      <c r="A61" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B61" s="67" t="s">
+      <c r="B61" s="64" t="s">
         <v>593</v>
       </c>
-      <c r="C61" s="67" t="s">
+      <c r="C61" s="64" t="s">
         <v>594</v>
       </c>
-      <c r="D61" s="67" t="s">
+      <c r="D61" s="64" t="s">
         <v>595</v>
       </c>
-      <c r="E61" s="67" t="s">
+      <c r="E61" s="64" t="s">
         <v>596</v>
       </c>
-      <c r="F61" s="67" t="s">
+      <c r="F61" s="64" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="62" ht="64" customHeight="1" spans="1:14">
-      <c r="A62" s="68">
+      <c r="A62" s="65">
         <v>1</v>
       </c>
       <c r="B62" s="4" t="s">
@@ -15389,7 +15343,7 @@
       </c>
     </row>
     <row r="63" ht="64" customHeight="1" spans="1:14">
-      <c r="A63" s="69">
+      <c r="A63" s="66">
         <v>2</v>
       </c>
       <c r="B63" s="12" t="s">
@@ -15409,7 +15363,7 @@
       </c>
     </row>
     <row r="64" ht="64" customHeight="1" spans="1:14">
-      <c r="A64" s="69">
+      <c r="A64" s="66">
         <v>3</v>
       </c>
       <c r="B64" s="12" t="s">
@@ -15429,7 +15383,7 @@
       </c>
     </row>
     <row r="65" ht="64" customHeight="1" spans="1:14">
-      <c r="A65" s="69">
+      <c r="A65" s="66">
         <v>4</v>
       </c>
       <c r="B65" s="12" t="s">
@@ -15449,7 +15403,7 @@
       </c>
     </row>
     <row r="66" ht="64" customHeight="1" spans="1:14">
-      <c r="A66" s="70">
+      <c r="A66" s="67">
         <v>5</v>
       </c>
       <c r="B66" s="22" t="s">
@@ -15487,27 +15441,27 @@
       <c r="N69" s="29"/>
     </row>
     <row r="70" ht="34" customHeight="1" spans="1:14">
-      <c r="A70" s="71" t="s">
+      <c r="A70" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="71" t="s">
+      <c r="B70" s="68" t="s">
         <v>624</v>
       </c>
-      <c r="C70" s="71" t="s">
+      <c r="C70" s="68" t="s">
         <v>625</v>
       </c>
-      <c r="D70" s="71" t="s">
+      <c r="D70" s="68" t="s">
         <v>626</v>
       </c>
-      <c r="E70" s="71" t="s">
+      <c r="E70" s="68" t="s">
         <v>627</v>
       </c>
-      <c r="F70" s="71" t="s">
+      <c r="F70" s="68" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="71" ht="64" customHeight="1" spans="1:14">
-      <c r="A71" s="68">
+      <c r="A71" s="65">
         <v>1</v>
       </c>
       <c r="B71" s="4" t="s">
@@ -15527,7 +15481,7 @@
       </c>
     </row>
     <row r="72" ht="64" customHeight="1" spans="1:14">
-      <c r="A72" s="69">
+      <c r="A72" s="66">
         <v>2</v>
       </c>
       <c r="B72" s="12" t="s">
@@ -15547,7 +15501,7 @@
       </c>
     </row>
     <row r="73" ht="64" customHeight="1" spans="1:14">
-      <c r="A73" s="69">
+      <c r="A73" s="66">
         <v>3</v>
       </c>
       <c r="B73" s="12" t="s">
@@ -15567,7 +15521,7 @@
       </c>
     </row>
     <row r="74" ht="64" customHeight="1" spans="1:14">
-      <c r="A74" s="70">
+      <c r="A74" s="67">
         <v>4</v>
       </c>
       <c r="B74" s="22" t="s">
@@ -15587,38 +15541,38 @@
       </c>
     </row>
     <row r="76" ht="30" customHeight="1" spans="1:14">
-      <c r="A76" s="72" t="s">
+      <c r="A76" s="69" t="s">
         <v>654</v>
       </c>
-      <c r="B76" s="73"/>
-      <c r="C76" s="73"/>
-      <c r="D76" s="73"/>
-      <c r="E76" s="73"/>
-      <c r="F76" s="73"/>
-      <c r="G76" s="74"/>
-      <c r="H76" s="74"/>
-      <c r="I76" s="74"/>
-      <c r="J76" s="74"/>
-      <c r="K76" s="74"/>
-      <c r="L76" s="74"/>
-      <c r="M76" s="74"/>
-      <c r="N76" s="75"/>
+      <c r="B76" s="70"/>
+      <c r="C76" s="70"/>
+      <c r="D76" s="70"/>
+      <c r="E76" s="70"/>
+      <c r="F76" s="70"/>
+      <c r="G76" s="71"/>
+      <c r="H76" s="71"/>
+      <c r="I76" s="71"/>
+      <c r="J76" s="71"/>
+      <c r="K76" s="71"/>
+      <c r="L76" s="71"/>
+      <c r="M76" s="71"/>
+      <c r="N76" s="71"/>
     </row>
     <row r="77" ht="30" customHeight="1" spans="1:14">
-      <c r="A77" s="76"/>
-      <c r="B77" s="77"/>
-      <c r="C77" s="77"/>
-      <c r="D77" s="77"/>
-      <c r="E77" s="77"/>
-      <c r="F77" s="77"/>
-      <c r="G77" s="78"/>
-      <c r="H77" s="78"/>
-      <c r="I77" s="78"/>
-      <c r="J77" s="78"/>
-      <c r="K77" s="78"/>
-      <c r="L77" s="78"/>
-      <c r="M77" s="78"/>
-      <c r="N77" s="79"/>
+      <c r="A77" s="72"/>
+      <c r="B77" s="73"/>
+      <c r="C77" s="73"/>
+      <c r="D77" s="73"/>
+      <c r="E77" s="73"/>
+      <c r="F77" s="73"/>
+      <c r="G77" s="71"/>
+      <c r="H77" s="71"/>
+      <c r="I77" s="71"/>
+      <c r="J77" s="71"/>
+      <c r="K77" s="71"/>
+      <c r="L77" s="71"/>
+      <c r="M77" s="71"/>
+      <c r="N77" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -16273,23 +16227,23 @@
       <c r="K54" s="61"/>
       <c r="L54" s="61"/>
       <c r="M54" s="61"/>
-      <c r="N54" s="62"/>
+      <c r="N54" s="61"/>
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:14">
-      <c r="A55" s="63"/>
-      <c r="B55" s="64"/>
-      <c r="C55" s="64"/>
-      <c r="D55" s="64"/>
-      <c r="E55" s="64"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="65"/>
-      <c r="H55" s="65"/>
-      <c r="I55" s="65"/>
-      <c r="J55" s="65"/>
-      <c r="K55" s="65"/>
-      <c r="L55" s="65"/>
-      <c r="M55" s="65"/>
-      <c r="N55" s="66"/>
+      <c r="A55" s="62"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="61"/>
+      <c r="I55" s="61"/>
+      <c r="J55" s="61"/>
+      <c r="K55" s="61"/>
+      <c r="L55" s="61"/>
+      <c r="M55" s="61"/>
+      <c r="N55" s="61"/>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:14">
       <c r="A57" s="44" t="s">
@@ -16310,27 +16264,27 @@
       <c r="N57" s="29"/>
     </row>
     <row r="58" ht="34" customHeight="1" spans="1:14">
-      <c r="A58" s="67" t="s">
+      <c r="A58" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B58" s="67" t="s">
+      <c r="B58" s="64" t="s">
         <v>593</v>
       </c>
-      <c r="C58" s="67" t="s">
+      <c r="C58" s="64" t="s">
         <v>594</v>
       </c>
-      <c r="D58" s="67" t="s">
+      <c r="D58" s="64" t="s">
         <v>595</v>
       </c>
-      <c r="E58" s="67" t="s">
+      <c r="E58" s="64" t="s">
         <v>596</v>
       </c>
-      <c r="F58" s="67" t="s">
+      <c r="F58" s="64" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="59" ht="64" customHeight="1" spans="1:14">
-      <c r="A59" s="68">
+      <c r="A59" s="65">
         <v>1</v>
       </c>
       <c r="B59" s="4" t="s">
@@ -16350,7 +16304,7 @@
       </c>
     </row>
     <row r="60" ht="64" customHeight="1" spans="1:14">
-      <c r="A60" s="69">
+      <c r="A60" s="66">
         <v>2</v>
       </c>
       <c r="B60" s="12" t="s">
@@ -16370,7 +16324,7 @@
       </c>
     </row>
     <row r="61" ht="64" customHeight="1" spans="1:14">
-      <c r="A61" s="70">
+      <c r="A61" s="67">
         <v>3</v>
       </c>
       <c r="B61" s="22" t="s">
@@ -16408,27 +16362,27 @@
       <c r="N64" s="29"/>
     </row>
     <row r="65" ht="34" customHeight="1" spans="1:14">
-      <c r="A65" s="71" t="s">
+      <c r="A65" s="68" t="s">
         <v>70</v>
       </c>
-      <c r="B65" s="71" t="s">
+      <c r="B65" s="68" t="s">
         <v>624</v>
       </c>
-      <c r="C65" s="71" t="s">
+      <c r="C65" s="68" t="s">
         <v>625</v>
       </c>
-      <c r="D65" s="71" t="s">
+      <c r="D65" s="68" t="s">
         <v>626</v>
       </c>
-      <c r="E65" s="71" t="s">
+      <c r="E65" s="68" t="s">
         <v>627</v>
       </c>
-      <c r="F65" s="71" t="s">
+      <c r="F65" s="68" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="66" ht="64" customHeight="1" spans="1:14">
-      <c r="A66" s="68">
+      <c r="A66" s="65">
         <v>1</v>
       </c>
       <c r="B66" s="4" t="s">
@@ -16448,7 +16402,7 @@
       </c>
     </row>
     <row r="67" ht="64" customHeight="1" spans="1:14">
-      <c r="A67" s="69">
+      <c r="A67" s="66">
         <v>2</v>
       </c>
       <c r="B67" s="12" t="s">
@@ -16468,7 +16422,7 @@
       </c>
     </row>
     <row r="68" ht="64" customHeight="1" spans="1:14">
-      <c r="A68" s="70">
+      <c r="A68" s="67">
         <v>3</v>
       </c>
       <c r="B68" s="22" t="s">
@@ -16488,38 +16442,38 @@
       </c>
     </row>
     <row r="70" ht="30" customHeight="1" spans="1:14">
-      <c r="A70" s="72" t="s">
+      <c r="A70" s="69" t="s">
         <v>654</v>
       </c>
-      <c r="B70" s="73"/>
-      <c r="C70" s="73"/>
-      <c r="D70" s="73"/>
-      <c r="E70" s="73"/>
-      <c r="F70" s="73"/>
-      <c r="G70" s="74"/>
-      <c r="H70" s="74"/>
-      <c r="I70" s="74"/>
-      <c r="J70" s="74"/>
-      <c r="K70" s="74"/>
-      <c r="L70" s="74"/>
-      <c r="M70" s="74"/>
-      <c r="N70" s="75"/>
+      <c r="B70" s="70"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="70"/>
+      <c r="E70" s="70"/>
+      <c r="F70" s="70"/>
+      <c r="G70" s="71"/>
+      <c r="H70" s="71"/>
+      <c r="I70" s="71"/>
+      <c r="J70" s="71"/>
+      <c r="K70" s="71"/>
+      <c r="L70" s="71"/>
+      <c r="M70" s="71"/>
+      <c r="N70" s="71"/>
     </row>
     <row r="71" ht="30" customHeight="1" spans="1:14">
-      <c r="A71" s="76"/>
-      <c r="B71" s="77"/>
-      <c r="C71" s="77"/>
-      <c r="D71" s="77"/>
-      <c r="E71" s="77"/>
-      <c r="F71" s="77"/>
-      <c r="G71" s="78"/>
-      <c r="H71" s="78"/>
-      <c r="I71" s="78"/>
-      <c r="J71" s="78"/>
-      <c r="K71" s="78"/>
-      <c r="L71" s="78"/>
-      <c r="M71" s="78"/>
-      <c r="N71" s="79"/>
+      <c r="A71" s="72"/>
+      <c r="B71" s="73"/>
+      <c r="C71" s="73"/>
+      <c r="D71" s="73"/>
+      <c r="E71" s="73"/>
+      <c r="F71" s="73"/>
+      <c r="G71" s="71"/>
+      <c r="H71" s="71"/>
+      <c r="I71" s="71"/>
+      <c r="J71" s="71"/>
+      <c r="K71" s="71"/>
+      <c r="L71" s="71"/>
+      <c r="M71" s="71"/>
+      <c r="N71" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="6">
